--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A2C8D6-055E-4D61-B134-A3031FE172D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C759C882-21E2-4F14-8D22-3D274A559D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3341" uniqueCount="1677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3361" uniqueCount="1687">
   <si>
     <t>ت</t>
   </si>
@@ -5256,6 +5256,36 @@
   </si>
   <si>
     <t>اعمال لبخ دار 86-83 قائمة 95-97</t>
+  </si>
+  <si>
+    <t>657</t>
+  </si>
+  <si>
+    <t>علاء إبراهيم بادي</t>
+  </si>
+  <si>
+    <t>ZA5-106</t>
+  </si>
+  <si>
+    <t>1985</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تسليم دار -132 قائمة90   </t>
+  </si>
+  <si>
+    <t>1986</t>
+  </si>
+  <si>
+    <t>رياض نوري العبدان</t>
+  </si>
+  <si>
+    <t>تجهيز اسمنت 19 طن - تك رمل عدد 6</t>
+  </si>
+  <si>
+    <t>1987</t>
+  </si>
+  <si>
+    <t>1988</t>
   </si>
 </sst>
 </file>
@@ -5633,7 +5663,7 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="58">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6115,6 +6145,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6361,18 +6401,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -26641,7 +26681,6 @@
       <c r="H833" s="12">
         <v>2000000</v>
       </c>
-      <c r="I833" s="43"/>
     </row>
     <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" s="18">
@@ -26666,7 +26705,6 @@
         <v>180000</v>
       </c>
       <c r="H834" s="40"/>
-      <c r="I834" s="43"/>
     </row>
     <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" s="18">
@@ -26691,67 +26729,131 @@
         <v>1000000</v>
       </c>
       <c r="H835" s="40"/>
-      <c r="I835" s="43"/>
-    </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" s="18">
         <v>835</v>
       </c>
-      <c r="B836" s="7"/>
-      <c r="C836" s="8"/>
-      <c r="D836" s="8"/>
-      <c r="E836" s="18"/>
-      <c r="F836" s="18"/>
-      <c r="G836" s="12"/>
-      <c r="H836" s="13"/>
+      <c r="B836" s="7" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C836" s="8">
+        <v>46286</v>
+      </c>
+      <c r="D836" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E836" s="18" t="s">
+        <v>1678</v>
+      </c>
+      <c r="F836" s="32" t="s">
+        <v>1679</v>
+      </c>
+      <c r="G836" s="18"/>
+      <c r="H836" s="12">
+        <v>6000000</v>
+      </c>
+      <c r="I836" s="43"/>
     </row>
     <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" s="18">
         <v>836</v>
       </c>
-      <c r="B837" s="7"/>
-      <c r="C837" s="8"/>
-      <c r="D837" s="8"/>
-      <c r="E837" s="18"/>
-      <c r="F837" s="18"/>
-      <c r="G837" s="12"/>
-      <c r="H837" s="13"/>
+      <c r="B837" s="7" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C837" s="8">
+        <v>46286</v>
+      </c>
+      <c r="D837" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E837" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F837" s="18" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G837" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H837" s="40"/>
+      <c r="I837" s="43"/>
     </row>
     <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" s="18">
         <v>837</v>
       </c>
-      <c r="B838" s="7"/>
-      <c r="C838" s="8"/>
-      <c r="D838" s="8"/>
-      <c r="E838" s="18"/>
-      <c r="F838" s="18"/>
-      <c r="G838" s="12"/>
-      <c r="H838" s="13"/>
+      <c r="B838" s="7" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C838" s="8">
+        <v>46286</v>
+      </c>
+      <c r="D838" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E838" s="18" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F838" s="18" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G838" s="12">
+        <v>3000000</v>
+      </c>
+      <c r="H838" s="40"/>
+      <c r="I838" s="43"/>
     </row>
     <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" s="18">
         <v>838</v>
       </c>
-      <c r="B839" s="7"/>
-      <c r="C839" s="8"/>
-      <c r="D839" s="8"/>
-      <c r="E839" s="18"/>
-      <c r="F839" s="18"/>
-      <c r="G839" s="12"/>
-      <c r="H839" s="13"/>
+      <c r="B839" s="7" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C839" s="8">
+        <v>46286</v>
+      </c>
+      <c r="D839" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E839" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="F839" s="18" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G839" s="12">
+        <v>2500000</v>
+      </c>
+      <c r="H839" s="40"/>
+      <c r="I839" s="43"/>
     </row>
     <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" s="18">
         <v>839</v>
       </c>
-      <c r="B840" s="7"/>
-      <c r="C840" s="8"/>
-      <c r="D840" s="8"/>
-      <c r="E840" s="18"/>
-      <c r="F840" s="18"/>
-      <c r="G840" s="12"/>
-      <c r="H840" s="13"/>
+      <c r="B840" s="7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C840" s="8">
+        <v>46286</v>
+      </c>
+      <c r="D840" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E840" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="F840" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="G840" s="12">
+        <v>20000</v>
+      </c>
+      <c r="H840" s="40"/>
+      <c r="I840" s="43"/>
     </row>
     <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" s="18">
@@ -27739,198 +27841,201 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="44" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="43" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="42" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="41" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="40" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="38" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="37" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="36" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="36" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="35" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="34" priority="14"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="34" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="33" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="32" priority="7"/>
+  <conditionalFormatting sqref="B825:B832">
+    <cfRule type="duplicateValues" dxfId="32" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="31" priority="3"/>
+  <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="31" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="30" priority="209" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="211" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="29" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="70" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="28" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="80" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="27" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="88" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="26" priority="286" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="288" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="25" priority="204" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="206" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="24" priority="378" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="380" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="23" priority="379" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="381" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="22" priority="380" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="382" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="21" priority="381" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="383" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="20" priority="382" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="384" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="19" priority="645" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="647" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="18" priority="643" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="645" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="17" priority="649" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="651" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835">
-    <cfRule type="expression" dxfId="16" priority="651" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G840">
+    <cfRule type="expression" dxfId="16" priority="653" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="15" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="66" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="14" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="74" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="13" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="84" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="12" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="92" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="11" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="57" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="10" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="100" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="9" priority="465" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="467" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="8" priority="466" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="468" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="7" priority="467" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="469" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="6" priority="468" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="470" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="5" priority="469" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="471" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="4" priority="647" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="649" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="3" priority="650" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="652" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="2" priority="642" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="644" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H825 H833">
-    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
+  <conditionalFormatting sqref="H825 H833 H836">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B833:B835">
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C759C882-21E2-4F14-8D22-3D274A559D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5839AE0C-C59F-4456-A01B-A4035DF47AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3361" uniqueCount="1687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3377" uniqueCount="1692">
   <si>
     <t>ت</t>
   </si>
@@ -5286,6 +5286,21 @@
   </si>
   <si>
     <t>1988</t>
+  </si>
+  <si>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>658</t>
+  </si>
+  <si>
+    <t>1990</t>
+  </si>
+  <si>
+    <t>660</t>
+  </si>
+  <si>
+    <t>ندئ علاء طالب</t>
   </si>
 </sst>
 </file>
@@ -5293,9 +5308,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;د.ع.‏&quot;_-;\-* #,##0\ &quot;د.ع.‏&quot;_-;_-* &quot;-&quot;\ &quot;د.ع.‏&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0\ [$د.ع.‏-801]_-;\-* #,##0\ [$د.ع.‏-801]_-;_-* &quot;-&quot;\ [$د.ع.‏-801]_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;د.ع.‏&quot;_-;\-* #,##0\ &quot;د.ع.‏&quot;_-;_-* &quot;-&quot;\ &quot;د.ع.‏&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0\ [$د.ع.‏-801]_-;\-* #,##0\ [$د.ع.‏-801]_-;_-* &quot;-&quot;\ [$د.ع.‏-801]_-;_-@_-"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -5552,19 +5567,19 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5583,13 +5598,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5625,7 +5640,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5640,8 +5655,8 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5663,17 +5678,7 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="58">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="59">
     <dxf>
       <font>
         <b/>
@@ -6155,6 +6160,26 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6186,7 +6211,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0\ [$د.ع.‏-801]_-;\-* #,##0\ [$د.ع.‏-801]_-;_-* &quot;-&quot;\ [$د.ع.‏-801]_-;_-@_-"/>
+      <numFmt numFmtId="166" formatCode="_-* #,##0\ [$د.ع.‏-801]_-;\-* #,##0\ [$د.ع.‏-801]_-;_-* &quot;-&quot;\ [$د.ع.‏-801]_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6252,7 +6277,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+      <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6276,7 +6301,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+      <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6401,18 +6426,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -26753,7 +26778,6 @@
       <c r="H836" s="12">
         <v>6000000</v>
       </c>
-      <c r="I836" s="43"/>
     </row>
     <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" s="18">
@@ -26778,7 +26802,6 @@
         <v>1000000</v>
       </c>
       <c r="H837" s="40"/>
-      <c r="I837" s="43"/>
     </row>
     <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" s="18">
@@ -26803,7 +26826,6 @@
         <v>3000000</v>
       </c>
       <c r="H838" s="40"/>
-      <c r="I838" s="43"/>
     </row>
     <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" s="18">
@@ -26828,7 +26850,6 @@
         <v>2500000</v>
       </c>
       <c r="H839" s="40"/>
-      <c r="I839" s="43"/>
     </row>
     <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" s="18">
@@ -26853,55 +26874,106 @@
         <v>20000</v>
       </c>
       <c r="H840" s="40"/>
-      <c r="I840" s="43"/>
     </row>
     <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" s="18">
         <v>840</v>
       </c>
-      <c r="B841" s="7"/>
-      <c r="C841" s="8"/>
-      <c r="D841" s="8"/>
-      <c r="E841" s="18"/>
-      <c r="F841" s="18"/>
-      <c r="G841" s="12"/>
-      <c r="H841" s="13"/>
-    </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B841" s="7" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C841" s="8">
+        <v>46289</v>
+      </c>
+      <c r="D841" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E841" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F841" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G841" s="12">
+        <v>360000</v>
+      </c>
+      <c r="H841" s="40"/>
+      <c r="I841" s="43"/>
+    </row>
+    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="18">
         <v>841</v>
       </c>
-      <c r="B842" s="7"/>
-      <c r="C842" s="8"/>
-      <c r="D842" s="8"/>
-      <c r="E842" s="18"/>
-      <c r="F842" s="18"/>
-      <c r="G842" s="12"/>
-      <c r="H842" s="13"/>
+      <c r="B842" s="7" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C842" s="8">
+        <v>46289</v>
+      </c>
+      <c r="D842" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E842" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="F842" s="32" t="s">
+        <v>614</v>
+      </c>
+      <c r="G842" s="18"/>
+      <c r="H842" s="12">
+        <v>4000000</v>
+      </c>
+      <c r="I842" s="43"/>
     </row>
     <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" s="18">
         <v>842</v>
       </c>
-      <c r="B843" s="7"/>
-      <c r="C843" s="8"/>
-      <c r="D843" s="8"/>
-      <c r="E843" s="18"/>
-      <c r="F843" s="18"/>
-      <c r="G843" s="12"/>
-      <c r="H843" s="13"/>
-    </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B843" s="7" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C843" s="8">
+        <v>46289</v>
+      </c>
+      <c r="D843" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E843" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="F843" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="G843" s="12">
+        <v>5000</v>
+      </c>
+      <c r="H843" s="40"/>
+      <c r="I843" s="43"/>
+    </row>
+    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="18">
         <v>843</v>
       </c>
-      <c r="B844" s="7"/>
-      <c r="C844" s="8"/>
-      <c r="D844" s="8"/>
-      <c r="E844" s="18"/>
-      <c r="F844" s="18"/>
-      <c r="G844" s="12"/>
-      <c r="H844" s="13"/>
+      <c r="B844" s="7" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C844" s="8">
+        <v>46289</v>
+      </c>
+      <c r="D844" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E844" s="18" t="s">
+        <v>1691</v>
+      </c>
+      <c r="F844" s="32" t="s">
+        <v>614</v>
+      </c>
+      <c r="G844" s="18"/>
+      <c r="H844" s="12">
+        <v>7000000</v>
+      </c>
+      <c r="I844" s="43"/>
     </row>
     <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" s="18">
@@ -27841,202 +27913,205 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="45" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="44" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="43" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="42" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="41" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="40" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="39" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="38" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="37" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="37" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="36" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="35" priority="16"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="35" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="34" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="33" priority="9"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="32" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="31" priority="4"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B841:B844">
+    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="30" priority="211" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="213" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="29" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="72" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="28" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="82" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="27" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="90" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="26" priority="288" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="290" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="25" priority="206" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="208" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="24" priority="380" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="382" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="23" priority="381" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="383" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="22" priority="382" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="384" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="21" priority="383" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="385" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="20" priority="384" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="386" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="19" priority="647" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="649" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="18" priority="645" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="647" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="17" priority="651" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="653" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G840">
-    <cfRule type="expression" dxfId="16" priority="653" stopIfTrue="1">
+  <conditionalFormatting sqref="G843 G824 G826:G832 G834:G835 G837:G841">
+    <cfRule type="expression" dxfId="15" priority="655" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="15" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="68" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="14" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="76" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="13" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="86" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="12" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="94" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="11" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="59" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="10" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="102" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="9" priority="467" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="469" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="8" priority="468" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="470" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="7" priority="469" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="471" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="6" priority="470" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="472" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="5" priority="471" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="473" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="4" priority="649" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="651" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="3" priority="652" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="654" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="2" priority="644" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="646" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H825 H833 H836">
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
+  <conditionalFormatting sqref="H825 H833 H836 H842 H844">
+    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="B310" r:id="rId1" display="\\" xr:uid="{F04BB08D-F26B-4EF6-A6AF-EFAD65C2B411}"/>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5839AE0C-C59F-4456-A01B-A4035DF47AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9511D06-8642-46BA-A04E-B84F29E1F4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3377" uniqueCount="1692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="1694">
   <si>
     <t>ت</t>
   </si>
@@ -5301,6 +5301,12 @@
   </si>
   <si>
     <t>ندئ علاء طالب</t>
+  </si>
+  <si>
+    <t>1992</t>
+  </si>
+  <si>
+    <t>تجهيز أبواب حديد</t>
   </si>
 </sst>
 </file>
@@ -5678,7 +5684,17 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="59">
+  <dxfs count="60">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -6426,18 +6442,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -26898,7 +26914,6 @@
         <v>360000</v>
       </c>
       <c r="H841" s="40"/>
-      <c r="I841" s="43"/>
     </row>
     <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="18">
@@ -26923,7 +26938,6 @@
       <c r="H842" s="12">
         <v>4000000</v>
       </c>
-      <c r="I842" s="43"/>
     </row>
     <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" s="18">
@@ -26948,7 +26962,6 @@
         <v>5000</v>
       </c>
       <c r="H843" s="40"/>
-      <c r="I843" s="43"/>
     </row>
     <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="18">
@@ -26973,19 +26986,31 @@
       <c r="H844" s="12">
         <v>7000000</v>
       </c>
-      <c r="I844" s="43"/>
     </row>
     <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" s="18">
         <v>844</v>
       </c>
-      <c r="B845" s="7"/>
-      <c r="C845" s="8"/>
-      <c r="D845" s="8"/>
-      <c r="E845" s="18"/>
-      <c r="F845" s="18"/>
-      <c r="G845" s="12"/>
-      <c r="H845" s="13"/>
+      <c r="B845" s="7" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C845" s="8">
+        <v>46289</v>
+      </c>
+      <c r="D845" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E845" s="18" t="s">
+        <v>675</v>
+      </c>
+      <c r="F845" s="18" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G845" s="12">
+        <v>2900000</v>
+      </c>
+      <c r="H845" s="40"/>
+      <c r="I845" s="43"/>
     </row>
     <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" s="18">
@@ -27913,205 +27938,208 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="46" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="45" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="44" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="43" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="42" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="41" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="40" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="39" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="38" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="38" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="37" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="36" priority="18"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="36" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="35" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="34" priority="11"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="33" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
+  <conditionalFormatting sqref="B841:B844">
     <cfRule type="duplicateValues" dxfId="31" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841:B844">
-    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="29" priority="213" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="215" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="28" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="74" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="27" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="84" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="26" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="92" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="25" priority="290" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="292" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="24" priority="208" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="210" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="23" priority="382" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="384" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="22" priority="383" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="385" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="21" priority="384" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="386" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="20" priority="385" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="387" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="19" priority="386" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="388" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="18" priority="649" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="651" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="17" priority="647" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="649" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="16" priority="653" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="655" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G843 G824 G826:G832 G834:G835 G837:G841">
-    <cfRule type="expression" dxfId="15" priority="655" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845">
+    <cfRule type="expression" dxfId="16" priority="657" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="14" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="70" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="13" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="78" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="12" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="88" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="11" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="96" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="10" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="61" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="9" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="104" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="8" priority="469" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="471" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="7" priority="470" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="472" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="6" priority="471" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="473" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="5" priority="472" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="474" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="4" priority="473" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="475" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="3" priority="651" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="653" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="2" priority="654" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="656" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="1" priority="646" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="648" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H825 H833 H836 H842 H844">
-    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="10" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B845">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="B310" r:id="rId1" display="\\" xr:uid="{F04BB08D-F26B-4EF6-A6AF-EFAD65C2B411}"/>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9511D06-8642-46BA-A04E-B84F29E1F4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD9432C-69DF-4947-B2A6-FBC7037A4052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="1694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="1699">
   <si>
     <t>ت</t>
   </si>
@@ -5307,6 +5307,21 @@
   </si>
   <si>
     <t>تجهيز أبواب حديد</t>
+  </si>
+  <si>
+    <t>1993</t>
+  </si>
+  <si>
+    <t>خلفة سيراميك - دار 70</t>
+  </si>
+  <si>
+    <t>1994</t>
+  </si>
+  <si>
+    <t>تنكر ماء 17 وصل فقط</t>
+  </si>
+  <si>
+    <t>1995</t>
   </si>
 </sst>
 </file>
@@ -5684,7 +5699,7 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="61">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6196,6 +6211,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6442,18 +6467,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="49"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27010,43 +27035,81 @@
         <v>2900000</v>
       </c>
       <c r="H845" s="40"/>
-      <c r="I845" s="43"/>
     </row>
     <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" s="18">
         <v>845</v>
       </c>
-      <c r="B846" s="7"/>
-      <c r="C846" s="8"/>
-      <c r="D846" s="8"/>
-      <c r="E846" s="18"/>
-      <c r="F846" s="18"/>
-      <c r="G846" s="12"/>
-      <c r="H846" s="13"/>
+      <c r="B846" s="7" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C846" s="8">
+        <v>46291</v>
+      </c>
+      <c r="D846" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E846" s="18" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F846" s="18" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G846" s="12">
+        <v>200000</v>
+      </c>
+      <c r="H846" s="40"/>
+      <c r="I846" s="43"/>
     </row>
     <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" s="18">
         <v>846</v>
       </c>
-      <c r="B847" s="7"/>
-      <c r="C847" s="8"/>
-      <c r="D847" s="8"/>
-      <c r="E847" s="18"/>
-      <c r="F847" s="18"/>
-      <c r="G847" s="12"/>
-      <c r="H847" s="13"/>
+      <c r="B847" s="7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C847" s="8">
+        <v>46291</v>
+      </c>
+      <c r="D847" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E847" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F847" s="18" t="s">
+        <v>1697</v>
+      </c>
+      <c r="G847" s="12">
+        <v>575000</v>
+      </c>
+      <c r="H847" s="40"/>
+      <c r="I847" s="43"/>
     </row>
     <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" s="18">
         <v>847</v>
       </c>
-      <c r="B848" s="7"/>
-      <c r="C848" s="8"/>
-      <c r="D848" s="8"/>
-      <c r="E848" s="18"/>
-      <c r="F848" s="18"/>
-      <c r="G848" s="12"/>
-      <c r="H848" s="13"/>
+      <c r="B848" s="7" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C848" s="8">
+        <v>46291</v>
+      </c>
+      <c r="D848" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E848" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="F848" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="G848" s="12">
+        <v>25000</v>
+      </c>
+      <c r="H848" s="40"/>
+      <c r="I848" s="43"/>
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" s="18">
@@ -27938,207 +28001,210 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="47" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="46" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="45" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="44" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="43" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="42" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="41" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="39" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="39" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="38" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="37" priority="20"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="37" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="36" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="35" priority="13"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="34" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="34" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="33" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
+  <conditionalFormatting sqref="B841:B844">
     <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841:B844">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="31" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="30" priority="215" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="217" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="29" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="76" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="28" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="86" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="27" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="94" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="26" priority="292" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="294" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="25" priority="210" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="212" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="24" priority="384" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="386" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="23" priority="385" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="387" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="22" priority="386" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="388" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="21" priority="387" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="389" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="20" priority="388" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="390" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="19" priority="651" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="653" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="18" priority="649" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="651" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="17" priority="655" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="657" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845">
-    <cfRule type="expression" dxfId="16" priority="657" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G848">
+    <cfRule type="expression" dxfId="16" priority="659" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="15" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="72" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="14" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="80" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="13" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="90" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="12" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="98" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="11" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="63" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="10" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="106" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="9" priority="471" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="473" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="8" priority="472" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="474" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="7" priority="473" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="475" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="6" priority="474" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="476" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="5" priority="475" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="477" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="4" priority="653" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="655" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="3" priority="656" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="658" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="2" priority="648" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="650" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H825 H833 H836 H842 H844">
-    <cfRule type="expression" dxfId="1" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="12" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B846:B848">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD9432C-69DF-4947-B2A6-FBC7037A4052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40948AD-0E3D-4EC5-88A0-11F57E5E9214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="1699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3409" uniqueCount="1706">
   <si>
     <t>ت</t>
   </si>
@@ -5322,6 +5322,27 @@
   </si>
   <si>
     <t>1995</t>
+  </si>
+  <si>
+    <t>1996</t>
+  </si>
+  <si>
+    <t>اعمال لبخ دار 130</t>
+  </si>
+  <si>
+    <t>1997</t>
+  </si>
+  <si>
+    <t>لارسا - محمد قاسم</t>
+  </si>
+  <si>
+    <t>سحب مبلغ لارسا - راتب الحارس محمد قاسم</t>
+  </si>
+  <si>
+    <t>1998</t>
+  </si>
+  <si>
+    <t>1999</t>
   </si>
 </sst>
 </file>
@@ -5699,7 +5720,7 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="62">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6221,6 +6242,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6467,18 +6498,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="61" dataDxfId="59" headerRowBorderDxfId="60" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -26724,7 +26755,7 @@
       </c>
       <c r="H832" s="40"/>
     </row>
-    <row r="833" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" s="18">
         <v>832</v>
       </c>
@@ -26748,7 +26779,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" s="18">
         <v>833</v>
       </c>
@@ -26772,7 +26803,7 @@
       </c>
       <c r="H834" s="40"/>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" s="18">
         <v>834</v>
       </c>
@@ -26796,7 +26827,7 @@
       </c>
       <c r="H835" s="40"/>
     </row>
-    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" s="18">
         <v>835</v>
       </c>
@@ -26820,7 +26851,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A837" s="18">
         <v>836</v>
       </c>
@@ -26844,7 +26875,7 @@
       </c>
       <c r="H837" s="40"/>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" s="18">
         <v>837</v>
       </c>
@@ -26868,7 +26899,7 @@
       </c>
       <c r="H838" s="40"/>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" s="18">
         <v>838</v>
       </c>
@@ -26892,7 +26923,7 @@
       </c>
       <c r="H839" s="40"/>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" s="18">
         <v>839</v>
       </c>
@@ -26916,7 +26947,7 @@
       </c>
       <c r="H840" s="40"/>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" s="18">
         <v>840</v>
       </c>
@@ -26940,7 +26971,7 @@
       </c>
       <c r="H841" s="40"/>
     </row>
-    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="18">
         <v>841</v>
       </c>
@@ -26964,7 +26995,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" s="18">
         <v>842</v>
       </c>
@@ -26988,7 +27019,7 @@
       </c>
       <c r="H843" s="40"/>
     </row>
-    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="18">
         <v>843</v>
       </c>
@@ -27012,7 +27043,7 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" s="18">
         <v>844</v>
       </c>
@@ -27036,7 +27067,7 @@
       </c>
       <c r="H845" s="40"/>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A846" s="18">
         <v>845</v>
       </c>
@@ -27059,9 +27090,8 @@
         <v>200000</v>
       </c>
       <c r="H846" s="40"/>
-      <c r="I846" s="43"/>
-    </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" s="18">
         <v>846</v>
       </c>
@@ -27084,9 +27114,8 @@
         <v>575000</v>
       </c>
       <c r="H847" s="40"/>
-      <c r="I847" s="43"/>
-    </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" s="18">
         <v>847</v>
       </c>
@@ -27109,57 +27138,108 @@
         <v>25000</v>
       </c>
       <c r="H848" s="40"/>
-      <c r="I848" s="43"/>
-    </row>
-    <row r="849" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" s="18">
         <v>848</v>
       </c>
-      <c r="B849" s="7"/>
-      <c r="C849" s="8"/>
-      <c r="D849" s="8"/>
-      <c r="E849" s="18"/>
-      <c r="F849" s="18"/>
-      <c r="G849" s="12"/>
-      <c r="H849" s="13"/>
-    </row>
-    <row r="850" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B849" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C849" s="8">
+        <v>46292</v>
+      </c>
+      <c r="D849" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E849" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F849" s="18" t="s">
+        <v>1700</v>
+      </c>
+      <c r="G849" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H849" s="40"/>
+      <c r="I849" s="43"/>
+    </row>
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" s="18">
         <v>849</v>
       </c>
-      <c r="B850" s="7"/>
-      <c r="C850" s="8"/>
-      <c r="D850" s="8"/>
-      <c r="E850" s="18"/>
-      <c r="F850" s="18"/>
-      <c r="G850" s="12"/>
-      <c r="H850" s="13"/>
-    </row>
-    <row r="851" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B850" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C850" s="8">
+        <v>46292</v>
+      </c>
+      <c r="D850" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E850" s="18" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F850" s="18" t="s">
+        <v>1703</v>
+      </c>
+      <c r="G850" s="12">
+        <v>450000</v>
+      </c>
+      <c r="H850" s="40"/>
+      <c r="I850" s="43"/>
+    </row>
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" s="18">
         <v>850</v>
       </c>
-      <c r="B851" s="7"/>
-      <c r="C851" s="8"/>
-      <c r="D851" s="8"/>
-      <c r="E851" s="18"/>
-      <c r="F851" s="18"/>
-      <c r="G851" s="12"/>
-      <c r="H851" s="13"/>
-    </row>
-    <row r="852" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B851" s="7" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C851" s="8">
+        <v>46292</v>
+      </c>
+      <c r="D851" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E851" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="F851" s="18" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G851" s="12">
+        <v>500000</v>
+      </c>
+      <c r="H851" s="40"/>
+      <c r="I851" s="43"/>
+    </row>
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" s="18">
         <v>851</v>
       </c>
-      <c r="B852" s="7"/>
-      <c r="C852" s="8"/>
-      <c r="D852" s="8"/>
-      <c r="E852" s="18"/>
-      <c r="F852" s="18"/>
-      <c r="G852" s="12"/>
-      <c r="H852" s="13"/>
-    </row>
-    <row r="853" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B852" s="7" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C852" s="8">
+        <v>46292</v>
+      </c>
+      <c r="D852" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E852" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F852" s="18" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G852" s="12">
+        <v>500000</v>
+      </c>
+      <c r="H852" s="40"/>
+      <c r="I852" s="43"/>
+    </row>
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" s="18">
         <v>852</v>
       </c>
@@ -27171,7 +27251,7 @@
       <c r="G853" s="12"/>
       <c r="H853" s="13"/>
     </row>
-    <row r="854" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" s="18">
         <v>853</v>
       </c>
@@ -27183,7 +27263,7 @@
       <c r="G854" s="12"/>
       <c r="H854" s="13"/>
     </row>
-    <row r="855" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" s="18">
         <v>854</v>
       </c>
@@ -27195,7 +27275,7 @@
       <c r="G855" s="12"/>
       <c r="H855" s="13"/>
     </row>
-    <row r="856" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" s="18">
         <v>855</v>
       </c>
@@ -27207,7 +27287,7 @@
       <c r="G856" s="12"/>
       <c r="H856" s="13"/>
     </row>
-    <row r="857" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" s="18">
         <v>856</v>
       </c>
@@ -27219,7 +27299,7 @@
       <c r="G857" s="12"/>
       <c r="H857" s="13"/>
     </row>
-    <row r="858" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" s="18">
         <v>857</v>
       </c>
@@ -27231,7 +27311,7 @@
       <c r="G858" s="12"/>
       <c r="H858" s="13"/>
     </row>
-    <row r="859" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" s="18">
         <v>858</v>
       </c>
@@ -27243,7 +27323,7 @@
       <c r="G859" s="12"/>
       <c r="H859" s="13"/>
     </row>
-    <row r="860" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" s="18">
         <v>859</v>
       </c>
@@ -27255,7 +27335,7 @@
       <c r="G860" s="12"/>
       <c r="H860" s="13"/>
     </row>
-    <row r="861" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" s="18">
         <v>860</v>
       </c>
@@ -27267,7 +27347,7 @@
       <c r="G861" s="12"/>
       <c r="H861" s="13"/>
     </row>
-    <row r="862" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" s="18">
         <v>861</v>
       </c>
@@ -27279,7 +27359,7 @@
       <c r="G862" s="12"/>
       <c r="H862" s="13"/>
     </row>
-    <row r="863" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" s="18">
         <v>862</v>
       </c>
@@ -27291,7 +27371,7 @@
       <c r="G863" s="12"/>
       <c r="H863" s="13"/>
     </row>
-    <row r="864" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" s="18">
         <v>863</v>
       </c>
@@ -28001,210 +28081,213 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="48" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="47" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="45" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="44" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="41" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="40" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="40" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="39" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="38" priority="22"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="38" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="37" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="36" priority="15"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="35" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="35" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="34" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
+  <conditionalFormatting sqref="B841:B844">
     <cfRule type="duplicateValues" dxfId="33" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841:B844">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B846:B848">
     <cfRule type="duplicateValues" dxfId="31" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="30" priority="217" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="219" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="29" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="78" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="28" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="88" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="27" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="96" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="26" priority="294" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="296" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="25" priority="212" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="214" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="24" priority="386" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="388" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="23" priority="387" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="389" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="22" priority="388" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="390" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="21" priority="389" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="391" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="20" priority="390" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="392" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="19" priority="653" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="655" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="18" priority="651" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="653" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="17" priority="657" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="659" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G848">
-    <cfRule type="expression" dxfId="16" priority="659" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G852">
+    <cfRule type="expression" dxfId="16" priority="661" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="15" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="74" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="14" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="82" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="13" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="92" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="12" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="100" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="11" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="65" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="10" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="108" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="9" priority="473" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="475" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="8" priority="474" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="476" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="7" priority="475" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="477" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="6" priority="476" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="478" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="5" priority="477" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="479" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="4" priority="655" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="657" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="3" priority="658" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="660" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="2" priority="650" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="652" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H825 H833 H836 H842 H844">
-    <cfRule type="expression" dxfId="1" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="14" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846:B848">
+  <conditionalFormatting sqref="B849:B852">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40948AD-0E3D-4EC5-88A0-11F57E5E9214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93373F18-469C-4C34-AA53-4E149002CEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3409" uniqueCount="1706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3417" uniqueCount="1709">
   <si>
     <t>ت</t>
   </si>
@@ -5343,6 +5343,15 @@
   </si>
   <si>
     <t>1999</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>تكمله ايجار البنايه</t>
   </si>
 </sst>
 </file>
@@ -5720,7 +5729,7 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="62">
+  <dxfs count="63">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6252,6 +6261,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6498,18 +6517,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="61" dataDxfId="59" headerRowBorderDxfId="60" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="53"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="52"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="50"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27162,7 +27181,6 @@
         <v>1000000</v>
       </c>
       <c r="H849" s="40"/>
-      <c r="I849" s="43"/>
     </row>
     <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" s="18">
@@ -27187,7 +27205,6 @@
         <v>450000</v>
       </c>
       <c r="H850" s="40"/>
-      <c r="I850" s="43"/>
     </row>
     <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" s="18">
@@ -27212,7 +27229,6 @@
         <v>500000</v>
       </c>
       <c r="H851" s="40"/>
-      <c r="I851" s="43"/>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" s="18">
@@ -27237,31 +27253,56 @@
         <v>500000</v>
       </c>
       <c r="H852" s="40"/>
-      <c r="I852" s="43"/>
     </row>
     <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" s="18">
         <v>852</v>
       </c>
-      <c r="B853" s="7"/>
-      <c r="C853" s="8"/>
-      <c r="D853" s="8"/>
-      <c r="E853" s="18"/>
-      <c r="F853" s="18"/>
-      <c r="G853" s="12"/>
-      <c r="H853" s="13"/>
+      <c r="B853" s="7" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C853" s="8">
+        <v>46293</v>
+      </c>
+      <c r="D853" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E853" s="18" t="s">
+        <v>984</v>
+      </c>
+      <c r="F853" s="18" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G853" s="12">
+        <v>5025000</v>
+      </c>
+      <c r="H853" s="40"/>
+      <c r="I853" s="43"/>
     </row>
     <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" s="18">
         <v>853</v>
       </c>
-      <c r="B854" s="7"/>
-      <c r="C854" s="8"/>
-      <c r="D854" s="8"/>
-      <c r="E854" s="18"/>
-      <c r="F854" s="18"/>
-      <c r="G854" s="12"/>
-      <c r="H854" s="13"/>
+      <c r="B854" s="7" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C854" s="8">
+        <v>46293</v>
+      </c>
+      <c r="D854" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E854" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="F854" s="18" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G854" s="12">
+        <v>525000</v>
+      </c>
+      <c r="H854" s="40"/>
+      <c r="I854" s="43"/>
     </row>
     <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" s="18">
@@ -28081,213 +28122,216 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="49" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="48" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="47" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="45" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="42" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="41" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="41" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="40" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="39" priority="24"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="39" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="38" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="37" priority="17"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="36" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="35" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
+  <conditionalFormatting sqref="B841:B844">
     <cfRule type="duplicateValues" dxfId="34" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841:B844">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="33" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B846:B848">
     <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846:B848">
+  <conditionalFormatting sqref="B849:B852">
     <cfRule type="duplicateValues" dxfId="31" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="30" priority="219" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="221" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="29" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="80" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="28" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="90" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="27" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="98" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="26" priority="296" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="298" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="25" priority="214" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="216" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="24" priority="388" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="390" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="23" priority="389" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="391" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="22" priority="390" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="392" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="21" priority="391" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="393" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="20" priority="392" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="394" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="19" priority="655" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="657" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="18" priority="653" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="655" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="17" priority="659" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="661" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G852">
-    <cfRule type="expression" dxfId="16" priority="661" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854">
+    <cfRule type="expression" dxfId="16" priority="663" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="15" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="76" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="14" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="84" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="13" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="94" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="12" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="102" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="11" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="67" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="10" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="110" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="9" priority="475" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="477" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="8" priority="476" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="478" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="7" priority="477" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="479" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="6" priority="478" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="480" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="5" priority="479" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="481" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="4" priority="657" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="659" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="3" priority="660" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="662" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="2" priority="652" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="654" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H825 H833 H836 H842 H844">
-    <cfRule type="expression" dxfId="1" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="16" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849:B852">
+  <conditionalFormatting sqref="B853:B854">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93373F18-469C-4C34-AA53-4E149002CEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F0CC8A-BE1A-4C83-8B73-478D5414B61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -5345,13 +5345,13 @@
     <t>1999</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
     <t>2001</t>
   </si>
   <si>
     <t>تكمله ايجار البنايه</t>
+  </si>
+  <si>
+    <t>2002</t>
   </si>
 </sst>
 </file>
@@ -5595,7 +5595,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5720,6 +5720,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -5729,7 +5730,18 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="64">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6517,18 +6529,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="63" dataDxfId="61" headerRowBorderDxfId="62" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="56"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27259,19 +27271,19 @@
         <v>852</v>
       </c>
       <c r="B853" s="7" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="C853" s="8">
         <v>46293</v>
       </c>
       <c r="D853" s="39" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="E853" s="18" t="s">
-        <v>984</v>
+        <v>124</v>
       </c>
       <c r="F853" s="18" t="s">
-        <v>1693</v>
+        <v>1444</v>
       </c>
       <c r="G853" s="12">
         <v>5025000</v>
@@ -27284,7 +27296,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="7" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="C854" s="8">
         <v>46293</v>
@@ -27296,7 +27308,7 @@
         <v>251</v>
       </c>
       <c r="F854" s="18" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="G854" s="12">
         <v>525000</v>
@@ -27313,7 +27325,7 @@
       <c r="D855" s="8"/>
       <c r="E855" s="18"/>
       <c r="F855" s="18"/>
-      <c r="G855" s="12"/>
+      <c r="G855" s="44"/>
       <c r="H855" s="13"/>
     </row>
     <row r="856" spans="1:9" x14ac:dyDescent="0.25">
@@ -28122,217 +28134,222 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="50" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="49" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="48" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="47" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="45" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="44" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="43" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="42" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="41" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="40" priority="26"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="40" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="39" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="38" priority="19"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="37" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="37" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="36" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
+  <conditionalFormatting sqref="B841:B844">
     <cfRule type="duplicateValues" dxfId="35" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841:B844">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="34" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B846:B848">
     <cfRule type="duplicateValues" dxfId="33" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846:B848">
+  <conditionalFormatting sqref="B849:B852">
     <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849:B852">
-    <cfRule type="duplicateValues" dxfId="31" priority="4"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="30" priority="221" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="223" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="29" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="82" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="28" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="92" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="27" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="100" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="26" priority="298" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="300" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="25" priority="216" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="218" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="24" priority="390" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="392" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="23" priority="391" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="393" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="22" priority="392" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="394" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="21" priority="393" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="395" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="20" priority="394" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="396" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="19" priority="657" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="659" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="18" priority="655" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="657" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="17" priority="661" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="663" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854">
-    <cfRule type="expression" dxfId="16" priority="663" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G853">
+    <cfRule type="expression" dxfId="17" priority="665" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="15" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="78" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="14" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="86" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="13" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="96" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="12" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="104" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="11" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="69" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="10" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="112" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="9" priority="477" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="479" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="8" priority="478" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="480" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="7" priority="479" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="481" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="6" priority="480" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="482" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="5" priority="481" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="483" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="4" priority="659" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="661" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="3" priority="662" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="664" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="2" priority="654" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="656" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H825 H833 H836 H842 H844">
-    <cfRule type="expression" dxfId="1" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="18" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853:B854">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G854">
+    <cfRule type="expression" dxfId="0" priority="677" stopIfTrue="1">
+      <formula>I854:I2853&gt;110000000</formula>
+    </cfRule>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="B310" r:id="rId1" display="\\" xr:uid="{F04BB08D-F26B-4EF6-A6AF-EFAD65C2B411}"/>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F0CC8A-BE1A-4C83-8B73-478D5414B61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE82E7C2-DBC2-4FD3-8C9E-D7869AE50413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3417" uniqueCount="1709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="1735">
   <si>
     <t>ت</t>
   </si>
@@ -5352,6 +5352,84 @@
   </si>
   <si>
     <t>2002</t>
+  </si>
+  <si>
+    <t>661</t>
+  </si>
+  <si>
+    <t>ZA5-71</t>
+  </si>
+  <si>
+    <t>662</t>
+  </si>
+  <si>
+    <t>ZA5-69</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>حسن عطشان خلف</t>
+  </si>
+  <si>
+    <t>دفعة صب كونكريت -داخل مجمع</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>حيدر عدنان</t>
+  </si>
+  <si>
+    <t>نجارة وحداده</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>664</t>
+  </si>
+  <si>
+    <t>665</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>احمد سمير محمد</t>
+  </si>
+  <si>
+    <t>عامل كهرباء</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>خلفة مخمر - دار 70 - قائمة 103</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>خلفة سيراميك - دار 68 - قائمة 111</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>سحب مباغ - تم تسليمه الى سيد عباس خليل محسن</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>اعمال لبخ - ت دار 87 - قائمة 98</t>
   </si>
 </sst>
 </file>
@@ -5595,7 +5673,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5720,7 +5798,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -5730,7 +5807,7 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="66">
     <dxf>
       <font>
         <b/>
@@ -5749,6 +5826,17 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6283,6 +6371,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6529,18 +6627,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="63" dataDxfId="61" headerRowBorderDxfId="62" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27289,7 +27387,6 @@
         <v>5025000</v>
       </c>
       <c r="H853" s="40"/>
-      <c r="I853" s="43"/>
     </row>
     <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" s="18">
@@ -27314,189 +27411,375 @@
         <v>525000</v>
       </c>
       <c r="H854" s="40"/>
-      <c r="I854" s="43"/>
-    </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" s="18">
         <v>854</v>
       </c>
-      <c r="B855" s="7"/>
-      <c r="C855" s="8"/>
-      <c r="D855" s="8"/>
-      <c r="E855" s="18"/>
-      <c r="F855" s="18"/>
-      <c r="G855" s="44"/>
-      <c r="H855" s="13"/>
-    </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B855" s="7" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C855" s="8">
+        <v>46294</v>
+      </c>
+      <c r="D855" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E855" s="18" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F855" s="32" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G855" s="18">
+        <v>9</v>
+      </c>
+      <c r="H855" s="12">
+        <v>5000000</v>
+      </c>
+      <c r="I855" s="43"/>
+    </row>
+    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" s="18">
         <v>855</v>
       </c>
-      <c r="B856" s="7"/>
-      <c r="C856" s="8"/>
-      <c r="D856" s="8"/>
-      <c r="E856" s="18"/>
-      <c r="F856" s="18"/>
-      <c r="G856" s="12"/>
-      <c r="H856" s="13"/>
+      <c r="B856" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C856" s="8">
+        <v>46294</v>
+      </c>
+      <c r="D856" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E856" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="F856" s="32" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G856" s="18">
+        <v>9</v>
+      </c>
+      <c r="H856" s="12">
+        <v>6000000</v>
+      </c>
+      <c r="I856" s="43"/>
     </row>
     <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" s="18">
         <v>856</v>
       </c>
-      <c r="B857" s="7"/>
-      <c r="C857" s="8"/>
-      <c r="D857" s="8"/>
-      <c r="E857" s="18"/>
-      <c r="F857" s="18"/>
-      <c r="G857" s="12"/>
-      <c r="H857" s="13"/>
+      <c r="B857" s="7" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C857" s="8">
+        <v>46294</v>
+      </c>
+      <c r="D857" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E857" s="18" t="s">
+        <v>1714</v>
+      </c>
+      <c r="F857" s="18" t="s">
+        <v>1715</v>
+      </c>
+      <c r="G857" s="12">
+        <v>5000000</v>
+      </c>
+      <c r="H857" s="40"/>
+      <c r="I857" s="43"/>
     </row>
     <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" s="18">
         <v>857</v>
       </c>
-      <c r="B858" s="7"/>
-      <c r="C858" s="8"/>
-      <c r="D858" s="8"/>
-      <c r="E858" s="18"/>
-      <c r="F858" s="18"/>
-      <c r="G858" s="12"/>
-      <c r="H858" s="13"/>
+      <c r="B858" s="7" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C858" s="8">
+        <v>46294</v>
+      </c>
+      <c r="D858" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E858" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="F858" s="18" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G858" s="12">
+        <v>2500000</v>
+      </c>
+      <c r="H858" s="40"/>
+      <c r="I858" s="43"/>
     </row>
     <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" s="18">
         <v>858</v>
       </c>
-      <c r="B859" s="7"/>
-      <c r="C859" s="8"/>
-      <c r="D859" s="8"/>
-      <c r="E859" s="18"/>
-      <c r="F859" s="18"/>
-      <c r="G859" s="12"/>
-      <c r="H859" s="13"/>
+      <c r="B859" s="7" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C859" s="8">
+        <v>46294</v>
+      </c>
+      <c r="D859" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E859" s="18" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F859" s="18" t="s">
+        <v>1719</v>
+      </c>
+      <c r="G859" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H859" s="40"/>
+      <c r="I859" s="43"/>
     </row>
     <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" s="18">
         <v>859</v>
       </c>
-      <c r="B860" s="7"/>
-      <c r="C860" s="8"/>
-      <c r="D860" s="8"/>
-      <c r="E860" s="18"/>
-      <c r="F860" s="18"/>
-      <c r="G860" s="12"/>
-      <c r="H860" s="13"/>
-    </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B860" s="7" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C860" s="8">
+        <v>46294</v>
+      </c>
+      <c r="D860" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E860" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F860" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="G860" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H860" s="40"/>
+      <c r="I860" s="43"/>
+    </row>
+    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" s="18">
         <v>860</v>
       </c>
-      <c r="B861" s="7"/>
-      <c r="C861" s="8"/>
-      <c r="D861" s="8"/>
-      <c r="E861" s="18"/>
-      <c r="F861" s="18"/>
-      <c r="G861" s="12"/>
-      <c r="H861" s="13"/>
-    </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B861" s="7" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C861" s="8">
+        <v>46296</v>
+      </c>
+      <c r="D861" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E861" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="F861" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="G861" s="12">
+        <v>6000000</v>
+      </c>
+      <c r="H861" s="40"/>
+      <c r="I861" s="43"/>
+    </row>
+    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" s="18">
         <v>861</v>
       </c>
-      <c r="B862" s="7"/>
-      <c r="C862" s="8"/>
-      <c r="D862" s="8"/>
-      <c r="E862" s="18"/>
-      <c r="F862" s="18"/>
-      <c r="G862" s="12"/>
-      <c r="H862" s="13"/>
+      <c r="B862" s="7" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C862" s="8">
+        <v>46296</v>
+      </c>
+      <c r="D862" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E862" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F862" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="G862" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="H862" s="40"/>
+      <c r="I862" s="43"/>
     </row>
     <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" s="18">
         <v>862</v>
       </c>
-      <c r="B863" s="7"/>
-      <c r="C863" s="8"/>
-      <c r="D863" s="8"/>
-      <c r="E863" s="18"/>
-      <c r="F863" s="18"/>
-      <c r="G863" s="12"/>
-      <c r="H863" s="13"/>
+      <c r="B863" s="7" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C863" s="8">
+        <v>46296</v>
+      </c>
+      <c r="D863" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E863" s="18" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F863" s="18" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G863" s="12">
+        <v>500000</v>
+      </c>
+      <c r="H863" s="40"/>
+      <c r="I863" s="43"/>
     </row>
     <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" s="18">
         <v>863</v>
       </c>
-      <c r="B864" s="7"/>
-      <c r="C864" s="8"/>
-      <c r="D864" s="8"/>
-      <c r="E864" s="18"/>
-      <c r="F864" s="18"/>
-      <c r="G864" s="12"/>
-      <c r="H864" s="13"/>
-    </row>
-    <row r="865" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B864" s="7" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C864" s="8">
+        <v>46296</v>
+      </c>
+      <c r="D864" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E864" s="18" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F864" s="18" t="s">
+        <v>1727</v>
+      </c>
+      <c r="G864" s="12">
+        <v>535000</v>
+      </c>
+      <c r="H864" s="40"/>
+      <c r="I864" s="43"/>
+    </row>
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" s="18">
         <v>864</v>
       </c>
-      <c r="B865" s="7"/>
-      <c r="C865" s="8"/>
-      <c r="D865" s="8"/>
-      <c r="E865" s="18"/>
-      <c r="F865" s="18"/>
-      <c r="G865" s="12"/>
-      <c r="H865" s="13"/>
-    </row>
-    <row r="866" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B865" s="7" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C865" s="8">
+        <v>46296</v>
+      </c>
+      <c r="D865" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E865" s="18" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F865" s="18" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G865" s="12">
+        <v>665000</v>
+      </c>
+      <c r="H865" s="40"/>
+      <c r="I865" s="43"/>
+    </row>
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" s="18">
         <v>865</v>
       </c>
-      <c r="B866" s="7"/>
-      <c r="C866" s="8"/>
-      <c r="D866" s="8"/>
-      <c r="E866" s="18"/>
-      <c r="F866" s="18"/>
-      <c r="G866" s="12"/>
-      <c r="H866" s="13"/>
-    </row>
-    <row r="867" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B866" s="7" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C866" s="8">
+        <v>46296</v>
+      </c>
+      <c r="D866" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E866" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F866" s="18" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G866" s="12">
+        <v>4500000</v>
+      </c>
+      <c r="H866" s="40"/>
+      <c r="I866" s="43"/>
+    </row>
+    <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" s="18">
         <v>866</v>
       </c>
-      <c r="B867" s="7"/>
-      <c r="C867" s="8"/>
-      <c r="D867" s="8"/>
-      <c r="E867" s="18"/>
-      <c r="F867" s="18"/>
-      <c r="G867" s="12"/>
-      <c r="H867" s="13"/>
-    </row>
-    <row r="868" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B867" s="7" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C867" s="8">
+        <v>46298</v>
+      </c>
+      <c r="D867" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E867" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="F867" s="32" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G867" s="12">
+        <v>200000</v>
+      </c>
+      <c r="H867" s="40"/>
+      <c r="I867" s="12"/>
+    </row>
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" s="18">
         <v>867</v>
       </c>
-      <c r="B868" s="7"/>
-      <c r="C868" s="8"/>
-      <c r="D868" s="8"/>
-      <c r="E868" s="18"/>
-      <c r="F868" s="18"/>
-      <c r="G868" s="12"/>
-      <c r="H868" s="13"/>
-    </row>
-    <row r="869" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B868" s="7" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C868" s="8">
+        <v>46298</v>
+      </c>
+      <c r="D868" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E868" s="18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F868" s="18" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G868" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H868" s="40"/>
+      <c r="I868" s="43"/>
+    </row>
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" s="18">
         <v>868</v>
       </c>
       <c r="B869" s="7"/>
       <c r="C869" s="8"/>
-      <c r="D869" s="8"/>
+      <c r="D869" s="39"/>
       <c r="E869" s="18"/>
       <c r="F869" s="18"/>
       <c r="G869" s="12"/>
-      <c r="H869" s="13"/>
-    </row>
-    <row r="870" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H869" s="40"/>
+      <c r="I869" s="43"/>
+    </row>
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" s="18">
         <v>869</v>
       </c>
@@ -27508,7 +27791,7 @@
       <c r="G870" s="12"/>
       <c r="H870" s="13"/>
     </row>
-    <row r="871" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" s="18">
         <v>870</v>
       </c>
@@ -27520,7 +27803,7 @@
       <c r="G871" s="12"/>
       <c r="H871" s="13"/>
     </row>
-    <row r="872" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" s="18">
         <v>871</v>
       </c>
@@ -27532,7 +27815,7 @@
       <c r="G872" s="12"/>
       <c r="H872" s="13"/>
     </row>
-    <row r="873" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" s="18">
         <v>872</v>
       </c>
@@ -27544,7 +27827,7 @@
       <c r="G873" s="12"/>
       <c r="H873" s="13"/>
     </row>
-    <row r="874" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" s="18">
         <v>873</v>
       </c>
@@ -27556,7 +27839,7 @@
       <c r="G874" s="12"/>
       <c r="H874" s="13"/>
     </row>
-    <row r="875" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" s="18">
         <v>874</v>
       </c>
@@ -27568,7 +27851,7 @@
       <c r="G875" s="12"/>
       <c r="H875" s="13"/>
     </row>
-    <row r="876" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" s="18">
         <v>875</v>
       </c>
@@ -27580,7 +27863,7 @@
       <c r="G876" s="12"/>
       <c r="H876" s="13"/>
     </row>
-    <row r="877" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" s="18">
         <v>876</v>
       </c>
@@ -27592,7 +27875,7 @@
       <c r="G877" s="12"/>
       <c r="H877" s="13"/>
     </row>
-    <row r="878" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" s="18">
         <v>877</v>
       </c>
@@ -27604,7 +27887,7 @@
       <c r="G878" s="12"/>
       <c r="H878" s="13"/>
     </row>
-    <row r="879" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" s="18">
         <v>878</v>
       </c>
@@ -27616,7 +27899,7 @@
       <c r="G879" s="12"/>
       <c r="H879" s="13"/>
     </row>
-    <row r="880" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" s="18">
         <v>879</v>
       </c>
@@ -28134,221 +28417,229 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="51" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="50" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="49" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="48" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="46" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="45" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="44" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="43" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
-    <cfRule type="duplicateValues" dxfId="42" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="41" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763:B823">
-    <cfRule type="duplicateValues" dxfId="40" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="39" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
+    <cfRule type="duplicateValues" dxfId="40" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="39" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="38" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B833:B835">
-    <cfRule type="duplicateValues" dxfId="37" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
-    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B841:B844">
-    <cfRule type="duplicateValues" dxfId="35" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="34" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846:B848">
-    <cfRule type="duplicateValues" dxfId="33" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849:B852">
-    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B853:B854">
+    <cfRule type="duplicateValues" dxfId="33" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="31" priority="223" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="226" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="30" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="85" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="29" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="95" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="28" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="103" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="27" priority="300" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="303" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="26" priority="218" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="221" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="25" priority="392" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="395" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="24" priority="393" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="396" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="23" priority="394" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="397" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="22" priority="395" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="398" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="21" priority="396" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="399" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="20" priority="659" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="662" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="19" priority="657" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="660" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="18" priority="663" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="666" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G853">
-    <cfRule type="expression" dxfId="17" priority="665" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868:G869">
+    <cfRule type="expression" dxfId="2" priority="668" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="16" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="81" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="15" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="89" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="14" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="99" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="13" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="107" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="12" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="72" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="11" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="115" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="10" priority="479" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="482" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="9" priority="480" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="483" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="8" priority="481" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="484" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="7" priority="482" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="485" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="6" priority="483" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="486" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="5" priority="661" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="664" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="4" priority="664" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="667" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="3" priority="656" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="659" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H825 H833 H836 H842 H844">
-    <cfRule type="expression" dxfId="2" priority="18" stopIfTrue="1">
+  <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856">
+    <cfRule type="expression" dxfId="4" priority="21" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B853:B854">
+  <conditionalFormatting sqref="B855:B869">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G854">
-    <cfRule type="expression" dxfId="0" priority="677" stopIfTrue="1">
-      <formula>I854:I2853&gt;110000000</formula>
+  <conditionalFormatting sqref="I867">
+    <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
+      <formula>I865:I2863&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G867:G868">
+    <cfRule type="expression" dxfId="0" priority="684" stopIfTrue="1">
+      <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE82E7C2-DBC2-4FD3-8C9E-D7869AE50413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60087F1-2104-4CC3-BB1C-943A8411B879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="1735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3508" uniqueCount="1754">
   <si>
     <t>ت</t>
   </si>
@@ -5430,6 +5430,63 @@
   </si>
   <si>
     <t>اعمال لبخ - ت دار 87 - قائمة 98</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>اعمال لبخ - 212 الف  قائمة 98 - و788 الف من قائمة 96</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1,000,000 د.ع.‏ </t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صب سقف - دار 133 - قائمة 104  </t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>فتح قالب دار 137 - قائمة 112</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سحب مبلغ - تم تسليمه الى كاظم شهد </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2,500,000 د.ع.‏ </t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 299,000 د.ع.‏ </t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>شراء وحده سكنية</t>
+  </si>
+  <si>
+    <t>الجوهره</t>
+  </si>
+  <si>
+    <t>شراء وحدة سكنيه المرقمه (ZA80-159) وصولاتها السابقه (136,223,224,1382)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28,000,000 د.ع.‏ </t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سحب مبلغ - مجمع الجوهره </t>
   </si>
 </sst>
 </file>
@@ -5673,7 +5730,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5798,6 +5855,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -5816,16 +5882,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6167,6 +6223,16 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -27268,7 +27334,7 @@
       </c>
       <c r="H848" s="40"/>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" s="18">
         <v>848</v>
       </c>
@@ -27292,7 +27358,7 @@
       </c>
       <c r="H849" s="40"/>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" s="18">
         <v>849</v>
       </c>
@@ -27316,7 +27382,7 @@
       </c>
       <c r="H850" s="40"/>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" s="18">
         <v>850</v>
       </c>
@@ -27340,7 +27406,7 @@
       </c>
       <c r="H851" s="40"/>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" s="18">
         <v>851</v>
       </c>
@@ -27364,7 +27430,7 @@
       </c>
       <c r="H852" s="40"/>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" s="18">
         <v>852</v>
       </c>
@@ -27388,7 +27454,7 @@
       </c>
       <c r="H853" s="40"/>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" s="18">
         <v>853</v>
       </c>
@@ -27412,7 +27478,7 @@
       </c>
       <c r="H854" s="40"/>
     </row>
-    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" s="18">
         <v>854</v>
       </c>
@@ -27437,9 +27503,8 @@
       <c r="H855" s="12">
         <v>5000000</v>
       </c>
-      <c r="I855" s="43"/>
-    </row>
-    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="856" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" s="18">
         <v>855</v>
       </c>
@@ -27464,9 +27529,8 @@
       <c r="H856" s="12">
         <v>6000000</v>
       </c>
-      <c r="I856" s="43"/>
-    </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" s="18">
         <v>856</v>
       </c>
@@ -27489,9 +27553,8 @@
         <v>5000000</v>
       </c>
       <c r="H857" s="40"/>
-      <c r="I857" s="43"/>
-    </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" s="18">
         <v>857</v>
       </c>
@@ -27514,9 +27577,8 @@
         <v>2500000</v>
       </c>
       <c r="H858" s="40"/>
-      <c r="I858" s="43"/>
-    </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" s="18">
         <v>858</v>
       </c>
@@ -27539,9 +27601,8 @@
         <v>1000000</v>
       </c>
       <c r="H859" s="40"/>
-      <c r="I859" s="43"/>
-    </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" s="18">
         <v>859</v>
       </c>
@@ -27564,9 +27625,8 @@
         <v>1000000</v>
       </c>
       <c r="H860" s="40"/>
-      <c r="I860" s="43"/>
-    </row>
-    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="861" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" s="18">
         <v>860</v>
       </c>
@@ -27589,9 +27649,8 @@
         <v>6000000</v>
       </c>
       <c r="H861" s="40"/>
-      <c r="I861" s="43"/>
-    </row>
-    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="862" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" s="18">
         <v>861</v>
       </c>
@@ -27614,9 +27673,8 @@
         <v>10000000</v>
       </c>
       <c r="H862" s="40"/>
-      <c r="I862" s="43"/>
-    </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A863" s="18">
         <v>862</v>
       </c>
@@ -27639,9 +27697,8 @@
         <v>500000</v>
       </c>
       <c r="H863" s="40"/>
-      <c r="I863" s="43"/>
-    </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" s="18">
         <v>863</v>
       </c>
@@ -27664,7 +27721,6 @@
         <v>535000</v>
       </c>
       <c r="H864" s="40"/>
-      <c r="I864" s="43"/>
     </row>
     <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" s="18">
@@ -27689,7 +27745,6 @@
         <v>665000</v>
       </c>
       <c r="H865" s="40"/>
-      <c r="I865" s="43"/>
     </row>
     <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" s="18">
@@ -27714,7 +27769,6 @@
         <v>4500000</v>
       </c>
       <c r="H866" s="40"/>
-      <c r="I866" s="43"/>
     </row>
     <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" s="18">
@@ -27764,92 +27818,181 @@
         <v>1000000</v>
       </c>
       <c r="H868" s="40"/>
-      <c r="I868" s="43"/>
     </row>
     <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" s="18">
         <v>868</v>
       </c>
-      <c r="B869" s="7"/>
-      <c r="C869" s="8"/>
-      <c r="D869" s="39"/>
-      <c r="E869" s="18"/>
-      <c r="F869" s="18"/>
-      <c r="G869" s="12"/>
-      <c r="H869" s="40"/>
+      <c r="B869" s="7" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C869" s="8">
+        <v>46299</v>
+      </c>
+      <c r="D869" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E869" s="18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F869" s="18" t="s">
+        <v>1736</v>
+      </c>
+      <c r="G869" s="31" t="s">
+        <v>1737</v>
+      </c>
+      <c r="H869" s="44"/>
       <c r="I869" s="43"/>
     </row>
     <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" s="18">
         <v>869</v>
       </c>
-      <c r="B870" s="7"/>
-      <c r="C870" s="8"/>
-      <c r="D870" s="8"/>
-      <c r="E870" s="18"/>
-      <c r="F870" s="18"/>
-      <c r="G870" s="12"/>
-      <c r="H870" s="13"/>
+      <c r="B870" s="7" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C870" s="8">
+        <v>46299</v>
+      </c>
+      <c r="D870" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E870" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F870" s="18" t="s">
+        <v>1739</v>
+      </c>
+      <c r="G870" s="31" t="s">
+        <v>1737</v>
+      </c>
+      <c r="H870" s="45"/>
+      <c r="I870" s="43"/>
     </row>
     <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" s="18">
         <v>870</v>
       </c>
-      <c r="B871" s="7"/>
-      <c r="C871" s="8"/>
-      <c r="D871" s="8"/>
-      <c r="E871" s="18"/>
-      <c r="F871" s="18"/>
-      <c r="G871" s="12"/>
-      <c r="H871" s="13"/>
+      <c r="B871" s="7" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C871" s="8">
+        <v>46299</v>
+      </c>
+      <c r="D871" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E871" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F871" s="18" t="s">
+        <v>1741</v>
+      </c>
+      <c r="G871" s="31" t="s">
+        <v>1737</v>
+      </c>
+      <c r="H871" s="45"/>
+      <c r="I871" s="43"/>
     </row>
     <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" s="18">
         <v>871</v>
       </c>
-      <c r="B872" s="7"/>
-      <c r="C872" s="8"/>
-      <c r="D872" s="8"/>
-      <c r="E872" s="18"/>
-      <c r="F872" s="18"/>
-      <c r="G872" s="12"/>
-      <c r="H872" s="13"/>
+      <c r="B872" s="7" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C872" s="8">
+        <v>46299</v>
+      </c>
+      <c r="D872" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E872" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F872" s="18" t="s">
+        <v>1743</v>
+      </c>
+      <c r="G872" s="31" t="s">
+        <v>1744</v>
+      </c>
+      <c r="H872" s="45"/>
+      <c r="I872" s="43"/>
     </row>
     <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" s="18">
         <v>872</v>
       </c>
-      <c r="B873" s="7"/>
-      <c r="C873" s="8"/>
-      <c r="D873" s="8"/>
-      <c r="E873" s="18"/>
-      <c r="F873" s="18"/>
-      <c r="G873" s="12"/>
-      <c r="H873" s="13"/>
+      <c r="B873" s="7" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C873" s="8">
+        <v>46299</v>
+      </c>
+      <c r="D873" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E873" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F873" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G873" s="31" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H873" s="45"/>
+      <c r="I873" s="43"/>
     </row>
     <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" s="18">
         <v>873</v>
       </c>
-      <c r="B874" s="7"/>
-      <c r="C874" s="8"/>
-      <c r="D874" s="8"/>
-      <c r="E874" s="18"/>
-      <c r="F874" s="18"/>
-      <c r="G874" s="12"/>
-      <c r="H874" s="13"/>
+      <c r="B874" s="7" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C874" s="8">
+        <v>46299</v>
+      </c>
+      <c r="D874" s="8" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E874" s="18" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F874" s="18" t="s">
+        <v>1750</v>
+      </c>
+      <c r="G874" s="46"/>
+      <c r="H874" s="31" t="s">
+        <v>1751</v>
+      </c>
+      <c r="I874" s="43"/>
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" s="18">
         <v>874</v>
       </c>
-      <c r="B875" s="7"/>
-      <c r="C875" s="8"/>
-      <c r="D875" s="8"/>
-      <c r="E875" s="18"/>
-      <c r="F875" s="18"/>
-      <c r="G875" s="12"/>
-      <c r="H875" s="13"/>
+      <c r="B875" s="7" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C875" s="8">
+        <v>46299</v>
+      </c>
+      <c r="D875" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E875" s="18" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F875" s="18" t="s">
+        <v>1753</v>
+      </c>
+      <c r="G875" s="31" t="s">
+        <v>1751</v>
+      </c>
+      <c r="H875" s="45"/>
+      <c r="I875" s="43"/>
     </row>
     <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" s="18">
@@ -27860,8 +28003,8 @@
       <c r="D876" s="8"/>
       <c r="E876" s="18"/>
       <c r="F876" s="18"/>
-      <c r="G876" s="12"/>
-      <c r="H876" s="13"/>
+      <c r="G876" s="46"/>
+      <c r="H876" s="45"/>
     </row>
     <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" s="18">
@@ -28479,166 +28622,166 @@
   <conditionalFormatting sqref="B853:B854">
     <cfRule type="duplicateValues" dxfId="33" priority="5"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B855:B869">
+    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="32" priority="226" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="226" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="31" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="85" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="30" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="95" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="29" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="103" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="28" priority="303" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="303" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="27" priority="221" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="221" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="26" priority="395" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="395" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="25" priority="396" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="396" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="24" priority="397" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="397" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="23" priority="398" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="398" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="22" priority="399" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="399" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="21" priority="662" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="662" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="20" priority="660" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="660" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="19" priority="666" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="666" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868:G869">
-    <cfRule type="expression" dxfId="2" priority="668" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868">
+    <cfRule type="expression" dxfId="17" priority="668" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G867:G868">
+    <cfRule type="expression" dxfId="16" priority="684" stopIfTrue="1">
+      <formula>I865:I2863&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="18" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="81" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="17" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="89" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="16" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="99" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="15" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="107" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="14" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="72" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="13" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="115" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="12" priority="482" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="482" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="11" priority="483" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="483" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="10" priority="484" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="484" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="9" priority="485" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="485" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="8" priority="486" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="486" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="7" priority="664" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="664" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="6" priority="667" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="667" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="5" priority="659" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="659" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856">
-    <cfRule type="expression" dxfId="4" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="21" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B855:B869">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I867">
-    <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
-      <formula>I865:I2863&gt;110000000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G867:G868">
-    <cfRule type="expression" dxfId="0" priority="684" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
       <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60087F1-2104-4CC3-BB1C-943A8411B879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1A0509-53A4-4076-A31A-AB77C88BDD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3508" uniqueCount="1754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="1762">
   <si>
     <t>ت</t>
   </si>
@@ -5487,6 +5487,30 @@
   </si>
   <si>
     <t xml:space="preserve">سحب مبلغ - مجمع الجوهره </t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>اعمال لبخ - دار 13- قائمة 102</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>سيد كرار</t>
+  </si>
+  <si>
+    <t>طابو</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مسلم محمد لفتة </t>
   </si>
 </sst>
 </file>
@@ -5730,7 +5754,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5854,7 +5878,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5864,6 +5887,8 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -5873,7 +5898,17 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="67">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -6693,18 +6728,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="55"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="57"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="56"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27841,8 +27876,7 @@
       <c r="G869" s="31" t="s">
         <v>1737</v>
       </c>
-      <c r="H869" s="44"/>
-      <c r="I869" s="43"/>
+      <c r="H869" s="43"/>
     </row>
     <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" s="18">
@@ -27866,8 +27900,7 @@
       <c r="G870" s="31" t="s">
         <v>1737</v>
       </c>
-      <c r="H870" s="45"/>
-      <c r="I870" s="43"/>
+      <c r="H870" s="44"/>
     </row>
     <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" s="18">
@@ -27891,8 +27924,7 @@
       <c r="G871" s="31" t="s">
         <v>1737</v>
       </c>
-      <c r="H871" s="45"/>
-      <c r="I871" s="43"/>
+      <c r="H871" s="44"/>
     </row>
     <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" s="18">
@@ -27916,8 +27948,7 @@
       <c r="G872" s="31" t="s">
         <v>1744</v>
       </c>
-      <c r="H872" s="45"/>
-      <c r="I872" s="43"/>
+      <c r="H872" s="44"/>
     </row>
     <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" s="18">
@@ -27941,8 +27972,7 @@
       <c r="G873" s="31" t="s">
         <v>1746</v>
       </c>
-      <c r="H873" s="45"/>
-      <c r="I873" s="43"/>
+      <c r="H873" s="44"/>
     </row>
     <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" s="18">
@@ -27963,11 +27993,10 @@
       <c r="F874" s="18" t="s">
         <v>1750</v>
       </c>
-      <c r="G874" s="46"/>
+      <c r="G874" s="45"/>
       <c r="H874" s="31" t="s">
         <v>1751</v>
       </c>
-      <c r="I874" s="43"/>
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" s="18">
@@ -27991,56 +28020,107 @@
       <c r="G875" s="31" t="s">
         <v>1751</v>
       </c>
-      <c r="H875" s="45"/>
-      <c r="I875" s="43"/>
+      <c r="H875" s="44"/>
     </row>
     <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" s="18">
         <v>875</v>
       </c>
-      <c r="B876" s="7"/>
-      <c r="C876" s="8"/>
-      <c r="D876" s="8"/>
-      <c r="E876" s="18"/>
-      <c r="F876" s="18"/>
-      <c r="G876" s="46"/>
-      <c r="H876" s="45"/>
+      <c r="B876" s="7" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C876" s="8">
+        <v>46300</v>
+      </c>
+      <c r="D876" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E876" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F876" s="18" t="s">
+        <v>1755</v>
+      </c>
+      <c r="G876" s="12">
+        <v>250000</v>
+      </c>
+      <c r="H876" s="40"/>
+      <c r="I876" s="46"/>
     </row>
     <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" s="18">
         <v>876</v>
       </c>
-      <c r="B877" s="7"/>
-      <c r="C877" s="8"/>
-      <c r="D877" s="8"/>
-      <c r="E877" s="18"/>
-      <c r="F877" s="18"/>
-      <c r="G877" s="12"/>
-      <c r="H877" s="13"/>
+      <c r="B877" s="7" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C877" s="8">
+        <v>46300</v>
+      </c>
+      <c r="D877" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E877" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F877" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G877" s="47">
+        <v>1400000</v>
+      </c>
+      <c r="H877" s="40"/>
+      <c r="I877" s="46"/>
     </row>
     <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" s="18">
         <v>877</v>
       </c>
-      <c r="B878" s="7"/>
-      <c r="C878" s="8"/>
-      <c r="D878" s="8"/>
-      <c r="E878" s="18"/>
-      <c r="F878" s="18"/>
-      <c r="G878" s="12"/>
-      <c r="H878" s="13"/>
+      <c r="B878" s="7" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C878" s="8">
+        <v>46300</v>
+      </c>
+      <c r="D878" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E878" s="18" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F878" s="18" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G878" s="47">
+        <v>22500000</v>
+      </c>
+      <c r="H878" s="40"/>
+      <c r="I878" s="46"/>
     </row>
     <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" s="18">
         <v>878</v>
       </c>
-      <c r="B879" s="7"/>
-      <c r="C879" s="8"/>
-      <c r="D879" s="8"/>
-      <c r="E879" s="18"/>
-      <c r="F879" s="18"/>
-      <c r="G879" s="12"/>
-      <c r="H879" s="13"/>
+      <c r="B879" s="7" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C879" s="8">
+        <v>46300</v>
+      </c>
+      <c r="D879" s="39" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E879" s="18" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F879" s="18" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G879" s="47"/>
+      <c r="H879" s="12">
+        <v>7500000</v>
+      </c>
+      <c r="I879" s="46"/>
     </row>
     <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" s="18">
@@ -28560,230 +28640,233 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="53" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="52" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="51" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="50" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="48" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="46" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="45" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="45" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="44" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="43" priority="31"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="43" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="42" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="41" priority="24"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="40" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="40" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="39" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
+  <conditionalFormatting sqref="B841:B844">
     <cfRule type="duplicateValues" dxfId="38" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841:B844">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="37" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B846:B848">
     <cfRule type="duplicateValues" dxfId="36" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846:B848">
+  <conditionalFormatting sqref="B849:B852">
     <cfRule type="duplicateValues" dxfId="35" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849:B852">
-    <cfRule type="duplicateValues" dxfId="34" priority="9"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B853:B854">
-    <cfRule type="duplicateValues" dxfId="33" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B855:B869">
-    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="31" priority="226" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="228" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="30" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="87" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="29" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="97" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="28" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="105" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="27" priority="303" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="305" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="26" priority="221" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="223" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="25" priority="395" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="397" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="24" priority="396" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="398" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="23" priority="397" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="399" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="22" priority="398" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="400" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="21" priority="399" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="401" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="20" priority="662" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="664" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="19" priority="660" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="662" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="18" priority="666" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="668" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868">
-    <cfRule type="expression" dxfId="17" priority="668" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868 G876:G878">
+    <cfRule type="expression" dxfId="18" priority="670" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G867:G868">
-    <cfRule type="expression" dxfId="16" priority="684" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="686" stopIfTrue="1">
       <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="15" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="83" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="14" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="91" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="13" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="101" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="12" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="109" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="11" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="74" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="10" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="117" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="9" priority="482" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="484" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="8" priority="483" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="485" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="7" priority="484" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="486" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="6" priority="485" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="487" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="5" priority="486" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="488" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="4" priority="664" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="666" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="3" priority="667" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="669" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="2" priority="659" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="661" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856">
-    <cfRule type="expression" dxfId="1" priority="21" stopIfTrue="1">
+  <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856 H879">
+    <cfRule type="expression" dxfId="2" priority="23" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I867">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
       <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B876:B879">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="B310" r:id="rId1" display="\\" xr:uid="{F04BB08D-F26B-4EF6-A6AF-EFAD65C2B411}"/>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1A0509-53A4-4076-A31A-AB77C88BDD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE522AD-92E7-4930-BCA3-1F27C4A609A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="1762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3528" uniqueCount="1764">
   <si>
     <t>ت</t>
   </si>
@@ -5511,6 +5511,12 @@
   </si>
   <si>
     <t xml:space="preserve">مسلم محمد لفتة </t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>احمد دحام نزال</t>
   </si>
 </sst>
 </file>
@@ -5754,7 +5760,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5888,7 +5894,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -5898,7 +5903,7 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="67">
+  <dxfs count="68">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6482,6 +6487,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6728,18 +6743,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="56"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="58"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="57"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -28045,7 +28060,6 @@
         <v>250000</v>
       </c>
       <c r="H876" s="40"/>
-      <c r="I876" s="46"/>
     </row>
     <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" s="18">
@@ -28066,11 +28080,10 @@
       <c r="F877" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G877" s="47">
+      <c r="G877" s="12">
         <v>1400000</v>
       </c>
       <c r="H877" s="40"/>
-      <c r="I877" s="46"/>
     </row>
     <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" s="18">
@@ -28091,11 +28104,10 @@
       <c r="F878" s="18" t="s">
         <v>1759</v>
       </c>
-      <c r="G878" s="47">
+      <c r="G878" s="12">
         <v>22500000</v>
       </c>
       <c r="H878" s="40"/>
-      <c r="I878" s="46"/>
     </row>
     <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" s="18">
@@ -28116,23 +28128,35 @@
       <c r="F879" s="18" t="s">
         <v>1538</v>
       </c>
-      <c r="G879" s="47"/>
+      <c r="G879" s="12"/>
       <c r="H879" s="12">
         <v>7500000</v>
       </c>
-      <c r="I879" s="46"/>
     </row>
     <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" s="18">
         <v>879</v>
       </c>
-      <c r="B880" s="7"/>
-      <c r="C880" s="8"/>
-      <c r="D880" s="8"/>
-      <c r="E880" s="18"/>
-      <c r="F880" s="18"/>
-      <c r="G880" s="12"/>
-      <c r="H880" s="13"/>
+      <c r="B880" s="7" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C880" s="8">
+        <v>46301</v>
+      </c>
+      <c r="D880" s="39" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E880" s="18" t="s">
+        <v>1763</v>
+      </c>
+      <c r="F880" s="18" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G880" s="18"/>
+      <c r="H880" s="12">
+        <v>5000000</v>
+      </c>
+      <c r="I880" s="46"/>
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" s="18">
@@ -28640,232 +28664,235 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="54" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="53" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="52" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="51" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="50" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="47" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="46" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="45" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="44" priority="33"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="44" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="43" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="42" priority="26"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="41" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="40" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
+  <conditionalFormatting sqref="B841:B844">
     <cfRule type="duplicateValues" dxfId="39" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841:B844">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="38" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B846:B848">
     <cfRule type="duplicateValues" dxfId="37" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846:B848">
+  <conditionalFormatting sqref="B849:B852">
     <cfRule type="duplicateValues" dxfId="36" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849:B852">
-    <cfRule type="duplicateValues" dxfId="35" priority="11"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B853:B854">
-    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B855:B869">
+    <cfRule type="duplicateValues" dxfId="34" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B876:B879">
     <cfRule type="duplicateValues" dxfId="33" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="32" priority="228" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="230" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="31" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="89" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="30" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="99" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="29" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="107" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="28" priority="305" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="307" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="27" priority="223" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="225" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="26" priority="397" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="399" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="25" priority="398" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="400" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="24" priority="399" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="401" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="23" priority="400" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="402" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="22" priority="401" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="403" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="21" priority="664" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="666" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="20" priority="662" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="664" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="19" priority="668" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="670" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868 G876:G878">
-    <cfRule type="expression" dxfId="18" priority="670" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="672" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G867:G868">
-    <cfRule type="expression" dxfId="17" priority="686" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="688" stopIfTrue="1">
       <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="16" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="85" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="15" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="93" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="14" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="103" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="13" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="111" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="12" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="76" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="11" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="119" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="10" priority="484" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="486" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="9" priority="485" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="487" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="8" priority="486" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="488" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="7" priority="487" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="489" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="6" priority="488" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="490" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="5" priority="666" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="668" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="4" priority="669" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="671" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="3" priority="661" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="663" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856 H879">
-    <cfRule type="expression" dxfId="2" priority="23" stopIfTrue="1">
+  <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856 H879:H880">
+    <cfRule type="expression" dxfId="2" priority="25" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I867">
-    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
       <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B876:B879">
+  <conditionalFormatting sqref="B880">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE522AD-92E7-4930-BCA3-1F27C4A609A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED02C54D-BA77-442D-8468-5EC1D96C5A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3528" uniqueCount="1764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="1767">
   <si>
     <t>ت</t>
   </si>
@@ -5517,6 +5517,15 @@
   </si>
   <si>
     <t>احمد دحام نزال</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>قبض مبلغ - صرف في وصل 2027</t>
+  </si>
+  <si>
+    <t>2027</t>
   </si>
 </sst>
 </file>
@@ -5903,7 +5912,7 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
+  <dxfs count="71">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6497,6 +6506,37 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -6743,18 +6783,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -28156,33 +28196,58 @@
       <c r="H880" s="12">
         <v>5000000</v>
       </c>
-      <c r="I880" s="46"/>
-    </row>
-    <row r="881" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" s="18">
         <v>880</v>
       </c>
-      <c r="B881" s="7"/>
-      <c r="C881" s="8"/>
-      <c r="D881" s="8"/>
-      <c r="E881" s="18"/>
-      <c r="F881" s="18"/>
-      <c r="G881" s="12"/>
-      <c r="H881" s="13"/>
-    </row>
-    <row r="882" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B881" s="7" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C881" s="8">
+        <v>46301</v>
+      </c>
+      <c r="D881" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E881" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F881" s="18" t="s">
+        <v>1765</v>
+      </c>
+      <c r="G881" s="18"/>
+      <c r="H881" s="12">
+        <v>5000000</v>
+      </c>
+      <c r="I881" s="46"/>
+    </row>
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" s="18">
         <v>881</v>
       </c>
-      <c r="B882" s="7"/>
-      <c r="C882" s="8"/>
-      <c r="D882" s="8"/>
-      <c r="E882" s="18"/>
-      <c r="F882" s="18"/>
-      <c r="G882" s="12"/>
-      <c r="H882" s="13"/>
-    </row>
-    <row r="883" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B882" s="7" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C882" s="8">
+        <v>46301</v>
+      </c>
+      <c r="D882" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E882" s="18" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F882" s="18" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G882" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="H882" s="40"/>
+      <c r="I882" s="46"/>
+    </row>
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" s="18">
         <v>882</v>
       </c>
@@ -28194,7 +28259,7 @@
       <c r="G883" s="12"/>
       <c r="H883" s="13"/>
     </row>
-    <row r="884" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" s="18">
         <v>883</v>
       </c>
@@ -28206,7 +28271,7 @@
       <c r="G884" s="12"/>
       <c r="H884" s="13"/>
     </row>
-    <row r="885" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" s="18">
         <v>755</v>
       </c>
@@ -28218,7 +28283,7 @@
       <c r="G885" s="12"/>
       <c r="H885" s="13"/>
     </row>
-    <row r="886" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" s="18">
         <v>755</v>
       </c>
@@ -28230,7 +28295,7 @@
       <c r="G886" s="12"/>
       <c r="H886" s="13"/>
     </row>
-    <row r="887" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" s="18">
         <v>755</v>
       </c>
@@ -28242,7 +28307,7 @@
       <c r="G887" s="12"/>
       <c r="H887" s="13"/>
     </row>
-    <row r="888" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" s="18">
         <v>755</v>
       </c>
@@ -28254,7 +28319,7 @@
       <c r="G888" s="12"/>
       <c r="H888" s="13"/>
     </row>
-    <row r="889" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" s="18">
         <v>755</v>
       </c>
@@ -28266,7 +28331,7 @@
       <c r="G889" s="12"/>
       <c r="H889" s="13"/>
     </row>
-    <row r="890" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" s="18">
         <v>755</v>
       </c>
@@ -28278,7 +28343,7 @@
       <c r="G890" s="12"/>
       <c r="H890" s="13"/>
     </row>
-    <row r="891" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" s="18">
         <v>755</v>
       </c>
@@ -28290,7 +28355,7 @@
       <c r="G891" s="12"/>
       <c r="H891" s="13"/>
     </row>
-    <row r="892" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" s="18">
         <v>755</v>
       </c>
@@ -28302,7 +28367,7 @@
       <c r="G892" s="12"/>
       <c r="H892" s="13"/>
     </row>
-    <row r="893" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" s="18">
         <v>755</v>
       </c>
@@ -28314,7 +28379,7 @@
       <c r="G893" s="12"/>
       <c r="H893" s="13"/>
     </row>
-    <row r="894" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" s="18">
         <v>755</v>
       </c>
@@ -28326,7 +28391,7 @@
       <c r="G894" s="12"/>
       <c r="H894" s="13"/>
     </row>
-    <row r="895" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" s="18">
         <v>755</v>
       </c>
@@ -28338,7 +28403,7 @@
       <c r="G895" s="12"/>
       <c r="H895" s="13"/>
     </row>
-    <row r="896" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" s="18">
         <v>755</v>
       </c>
@@ -28664,235 +28729,238 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="55" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="54" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="53" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="51" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="49" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
-    <cfRule type="duplicateValues" dxfId="48" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="47" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="47" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="46" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="45" priority="35"/>
+  <conditionalFormatting sqref="B763:B823">
+    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B763:B823">
+  <conditionalFormatting sqref="B824">
     <cfRule type="duplicateValues" dxfId="44" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="43" priority="28"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="42" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
+    <cfRule type="duplicateValues" dxfId="42" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836:B840">
     <cfRule type="duplicateValues" dxfId="41" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B836:B840">
+  <conditionalFormatting sqref="B841:B844">
     <cfRule type="duplicateValues" dxfId="40" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B841:B844">
+  <conditionalFormatting sqref="B845">
     <cfRule type="duplicateValues" dxfId="39" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B845">
+  <conditionalFormatting sqref="B846:B848">
     <cfRule type="duplicateValues" dxfId="38" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B846:B848">
+  <conditionalFormatting sqref="B849:B852">
     <cfRule type="duplicateValues" dxfId="37" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B849:B852">
-    <cfRule type="duplicateValues" dxfId="36" priority="13"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B853:B854">
-    <cfRule type="duplicateValues" dxfId="35" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B855:B869">
+    <cfRule type="duplicateValues" dxfId="35" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B876:B879">
     <cfRule type="duplicateValues" dxfId="34" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B876:B879">
+  <conditionalFormatting sqref="B880">
     <cfRule type="duplicateValues" dxfId="33" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="32" priority="230" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="232" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="31" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="91" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="30" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="101" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="29" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="109" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="28" priority="307" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="309" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="27" priority="225" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="227" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="26" priority="399" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="401" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="25" priority="400" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="402" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="24" priority="401" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="403" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="23" priority="402" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="404" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="22" priority="403" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="405" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="21" priority="666" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="668" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="20" priority="664" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="666" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="19" priority="670" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="672" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868 G876:G878">
-    <cfRule type="expression" dxfId="18" priority="672" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868 G876:G878 G882">
+    <cfRule type="expression" dxfId="18" priority="674" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G867:G868">
-    <cfRule type="expression" dxfId="17" priority="688" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="690" stopIfTrue="1">
       <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="16" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="87" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="15" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="95" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="14" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="105" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="13" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="113" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="12" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="78" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="11" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="121" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="10" priority="486" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="488" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="9" priority="487" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="489" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="8" priority="488" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="490" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="7" priority="489" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="491" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="6" priority="490" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="492" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="5" priority="668" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="670" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="4" priority="671" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="673" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="3" priority="663" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="665" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856 H879:H880">
-    <cfRule type="expression" dxfId="2" priority="25" stopIfTrue="1">
+  <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856 H879:H881">
+    <cfRule type="expression" dxfId="2" priority="27" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I867">
-    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="9" stopIfTrue="1">
       <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B880">
+  <conditionalFormatting sqref="B881:B882">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>

--- a/تدقيق حسابات الجوهره.xlsx
+++ b/تدقيق حسابات الجوهره.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED02C54D-BA77-442D-8468-5EC1D96C5A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E8E170-EFDB-49A3-AE87-2B2F2F8E6013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -220,12 +220,84 @@
         </r>
       </text>
     </comment>
+    <comment ref="F885" authorId="0" shapeId="0" xr:uid="{B70FFBEC-5965-45F0-83FD-74387E2E5450}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Mohamed PC1:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+تاكد من الامر دار وقائمة</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F886" authorId="0" shapeId="0" xr:uid="{E3218898-C5AC-4EB3-B00D-AF8721774E99}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Mohamed PC1:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+تاكد من حساباتهم ملاحجضه موجوده بجراره</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F888" authorId="0" shapeId="0" xr:uid="{61BA500E-E660-4051-988A-2475396D2D81}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Mohamed PC1:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+دور ع وصل موجود عندي ؟</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="1767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="1811">
   <si>
     <t>ت</t>
   </si>
@@ -5526,6 +5598,138 @@
   </si>
   <si>
     <t>2027</t>
+  </si>
+  <si>
+    <t>674</t>
+  </si>
+  <si>
+    <t>675</t>
+  </si>
+  <si>
+    <t>اسيل نصيف جاسم</t>
+  </si>
+  <si>
+    <t>ZA5-107</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t>اعمال لبخ - 130 - قائمة 102</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>اعمال لبخ - دار 84 - قائمة 96</t>
+  </si>
+  <si>
+    <t>2030</t>
+  </si>
+  <si>
+    <t>2031</t>
+  </si>
+  <si>
+    <t>2032</t>
+  </si>
+  <si>
+    <t>صب سقف دار -126,127 قائمة -107,108</t>
+  </si>
+  <si>
+    <t>2033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">راتب شهر الثامن </t>
+  </si>
+  <si>
+    <t>2034</t>
+  </si>
+  <si>
+    <t>676</t>
+  </si>
+  <si>
+    <t>علا مجيد ابراهيم</t>
+  </si>
+  <si>
+    <t>ZA7-133</t>
+  </si>
+  <si>
+    <t>677</t>
+  </si>
+  <si>
+    <t>هديل جبار حسب</t>
+  </si>
+  <si>
+    <t>ZA7-137</t>
+  </si>
+  <si>
+    <t>2035</t>
+  </si>
+  <si>
+    <t>راتب الشهر التاسع - موقع</t>
+  </si>
+  <si>
+    <t>2036</t>
+  </si>
+  <si>
+    <t>أجور محامي</t>
+  </si>
+  <si>
+    <t>2037</t>
+  </si>
+  <si>
+    <t>تسليم دار 135 - قائمة 116</t>
+  </si>
+  <si>
+    <t>2038</t>
+  </si>
+  <si>
+    <t>2039</t>
+  </si>
+  <si>
+    <t>2040</t>
+  </si>
+  <si>
+    <t>2041</t>
+  </si>
+  <si>
+    <t>2042</t>
+  </si>
+  <si>
+    <t>2043</t>
+  </si>
+  <si>
+    <t>لوسي المحمد</t>
+  </si>
+  <si>
+    <t>2044</t>
+  </si>
+  <si>
+    <t>2045</t>
+  </si>
+  <si>
+    <t>2046</t>
+  </si>
+  <si>
+    <t>وسام محمد عبد</t>
+  </si>
+  <si>
+    <t>تجديد اشتراك المولد</t>
+  </si>
+  <si>
+    <t>2047</t>
+  </si>
+  <si>
+    <t>2049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أجور نقل </t>
+  </si>
+  <si>
+    <t>2050</t>
+  </si>
+  <si>
+    <t>2051</t>
   </si>
 </sst>
 </file>
@@ -5537,7 +5741,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0\ [$د.ع.‏-801]_-;\-* #,##0\ [$د.ع.‏-801]_-;_-* &quot;-&quot;\ [$د.ع.‏-801]_-;_-@_-"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5679,6 +5883,14 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -5769,7 +5981,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5903,6 +6115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="20" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -5912,7 +6127,29 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="72">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6517,17 +6754,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -6783,18 +7009,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" headerRowCellStyle="20% - Accent3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I922" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" headerRowCellStyle="20% - Accent3">
   <autoFilter ref="A1:I922" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{62DB1777-5E75-4D4F-B249-7EC46C034FC4}" name="Column1" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -28220,7 +28446,6 @@
       <c r="H881" s="12">
         <v>5000000</v>
       </c>
-      <c r="I881" s="46"/>
     </row>
     <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" s="18">
@@ -28245,333 +28470,683 @@
         <v>10000000</v>
       </c>
       <c r="H882" s="40"/>
-      <c r="I882" s="46"/>
-    </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="883" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A883" s="18">
         <v>882</v>
       </c>
-      <c r="B883" s="7"/>
-      <c r="C883" s="8"/>
-      <c r="D883" s="8"/>
-      <c r="E883" s="18"/>
-      <c r="F883" s="18"/>
-      <c r="G883" s="12"/>
-      <c r="H883" s="13"/>
-    </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B883" s="7" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C883" s="8">
+        <v>46302</v>
+      </c>
+      <c r="D883" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E883" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F883" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="G883" s="18"/>
+      <c r="H883" s="12">
+        <v>3000000</v>
+      </c>
+      <c r="I883" s="46"/>
+    </row>
+    <row r="884" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A884" s="18">
         <v>883</v>
       </c>
-      <c r="B884" s="7"/>
-      <c r="C884" s="8"/>
-      <c r="D884" s="8"/>
-      <c r="E884" s="18"/>
-      <c r="F884" s="18"/>
-      <c r="G884" s="12"/>
-      <c r="H884" s="13"/>
+      <c r="B884" s="7" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C884" s="8">
+        <v>46303</v>
+      </c>
+      <c r="D884" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E884" s="18" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F884" s="32" t="s">
+        <v>1770</v>
+      </c>
+      <c r="G884" s="18"/>
+      <c r="H884" s="12">
+        <v>6000000</v>
+      </c>
+      <c r="I884" s="46"/>
     </row>
     <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" s="18">
         <v>755</v>
       </c>
-      <c r="B885" s="7"/>
-      <c r="C885" s="8"/>
-      <c r="D885" s="8"/>
-      <c r="E885" s="18"/>
-      <c r="F885" s="18"/>
-      <c r="G885" s="12"/>
-      <c r="H885" s="13"/>
+      <c r="B885" s="7" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C885" s="8">
+        <v>46303</v>
+      </c>
+      <c r="D885" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E885" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F885" s="18" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G885" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H885" s="40"/>
+      <c r="I885" s="46"/>
     </row>
     <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" s="18">
         <v>755</v>
       </c>
-      <c r="B886" s="7"/>
-      <c r="C886" s="8"/>
-      <c r="D886" s="8"/>
-      <c r="E886" s="18"/>
-      <c r="F886" s="18"/>
-      <c r="G886" s="12"/>
-      <c r="H886" s="13"/>
+      <c r="B886" s="7" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C886" s="8">
+        <v>46303</v>
+      </c>
+      <c r="D886" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E886" s="18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F886" s="18" t="s">
+        <v>1774</v>
+      </c>
+      <c r="G886" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H886" s="40"/>
+      <c r="I886" s="46"/>
     </row>
     <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" s="18">
         <v>755</v>
       </c>
-      <c r="B887" s="7"/>
-      <c r="C887" s="8"/>
-      <c r="D887" s="8"/>
-      <c r="E887" s="18"/>
-      <c r="F887" s="18"/>
-      <c r="G887" s="12"/>
-      <c r="H887" s="13"/>
+      <c r="B887" s="7" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C887" s="8">
+        <v>46303</v>
+      </c>
+      <c r="D887" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E887" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="F887" s="18" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G887" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="H887" s="47"/>
+      <c r="I887" s="46"/>
     </row>
     <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" s="18">
         <v>755</v>
       </c>
-      <c r="B888" s="7"/>
-      <c r="C888" s="8"/>
-      <c r="D888" s="8"/>
-      <c r="E888" s="18"/>
-      <c r="F888" s="18"/>
-      <c r="G888" s="12"/>
-      <c r="H888" s="13"/>
+      <c r="B888" s="7" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C888" s="8">
+        <v>46303</v>
+      </c>
+      <c r="D888" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E888" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F888" s="18" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G888" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H888" s="40"/>
+      <c r="I888" s="46"/>
     </row>
     <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" s="18">
         <v>755</v>
       </c>
-      <c r="B889" s="7"/>
-      <c r="C889" s="8"/>
-      <c r="D889" s="8"/>
-      <c r="E889" s="18"/>
-      <c r="F889" s="18"/>
-      <c r="G889" s="12"/>
-      <c r="H889" s="13"/>
+      <c r="B889" s="7" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C889" s="8">
+        <v>46303</v>
+      </c>
+      <c r="D889" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E889" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F889" s="18" t="s">
+        <v>1778</v>
+      </c>
+      <c r="G889" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H889" s="40"/>
+      <c r="I889" s="46"/>
     </row>
     <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" s="18">
         <v>755</v>
       </c>
-      <c r="B890" s="7"/>
-      <c r="C890" s="8"/>
-      <c r="D890" s="8"/>
-      <c r="E890" s="18"/>
-      <c r="F890" s="18"/>
-      <c r="G890" s="12"/>
-      <c r="H890" s="13"/>
+      <c r="B890" s="7" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C890" s="8">
+        <v>46303</v>
+      </c>
+      <c r="D890" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E890" s="18" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F890" s="18" t="s">
+        <v>1780</v>
+      </c>
+      <c r="G890" s="12">
+        <v>300000</v>
+      </c>
+      <c r="H890" s="40"/>
+      <c r="I890" s="46"/>
     </row>
     <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" s="18">
         <v>755</v>
       </c>
-      <c r="B891" s="7"/>
-      <c r="C891" s="8"/>
-      <c r="D891" s="8"/>
-      <c r="E891" s="18"/>
-      <c r="F891" s="18"/>
-      <c r="G891" s="12"/>
-      <c r="H891" s="13"/>
-    </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B891" s="7" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C891" s="8">
+        <v>46305</v>
+      </c>
+      <c r="D891" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E891" s="18" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F891" s="18" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G891" s="12">
+        <v>650000</v>
+      </c>
+      <c r="H891" s="40"/>
+      <c r="I891" s="46"/>
+    </row>
+    <row r="892" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A892" s="18">
         <v>755</v>
       </c>
-      <c r="B892" s="7"/>
-      <c r="C892" s="8"/>
-      <c r="D892" s="8"/>
-      <c r="E892" s="18"/>
-      <c r="F892" s="18"/>
-      <c r="G892" s="12"/>
-      <c r="H892" s="13"/>
-    </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B892" s="7" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C892" s="8">
+        <v>46305</v>
+      </c>
+      <c r="D892" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E892" s="18" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F892" s="32" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G892" s="18"/>
+      <c r="H892" s="12">
+        <v>7000000</v>
+      </c>
+      <c r="I892" s="46"/>
+    </row>
+    <row r="893" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A893" s="18">
         <v>755</v>
       </c>
-      <c r="B893" s="7"/>
-      <c r="C893" s="8"/>
-      <c r="D893" s="8"/>
-      <c r="E893" s="18"/>
-      <c r="F893" s="18"/>
-      <c r="G893" s="12"/>
-      <c r="H893" s="13"/>
+      <c r="B893" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C893" s="8">
+        <v>46305</v>
+      </c>
+      <c r="D893" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E893" s="18" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F893" s="32" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G893" s="18"/>
+      <c r="H893" s="12">
+        <v>7000000</v>
+      </c>
+      <c r="I893" s="46"/>
     </row>
     <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" s="18">
         <v>755</v>
       </c>
-      <c r="B894" s="7"/>
-      <c r="C894" s="8"/>
-      <c r="D894" s="8"/>
-      <c r="E894" s="18"/>
-      <c r="F894" s="18"/>
-      <c r="G894" s="12"/>
-      <c r="H894" s="13"/>
+      <c r="B894" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C894" s="8">
+        <v>46305</v>
+      </c>
+      <c r="D894" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E894" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F894" s="18" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G894" s="12">
+        <v>700000</v>
+      </c>
+      <c r="H894" s="40"/>
+      <c r="I894" s="46"/>
     </row>
     <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" s="18">
         <v>755</v>
       </c>
-      <c r="B895" s="7"/>
-      <c r="C895" s="8"/>
-      <c r="D895" s="8"/>
-      <c r="E895" s="18"/>
-      <c r="F895" s="18"/>
-      <c r="G895" s="12"/>
-      <c r="H895" s="13"/>
+      <c r="B895" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C895" s="8">
+        <v>46305</v>
+      </c>
+      <c r="D895" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E895" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="F895" s="18" t="s">
+        <v>1791</v>
+      </c>
+      <c r="G895" s="12">
+        <v>100000</v>
+      </c>
+      <c r="H895" s="40"/>
+      <c r="I895" s="46"/>
     </row>
     <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" s="18">
         <v>755</v>
       </c>
-      <c r="B896" s="7"/>
-      <c r="C896" s="8"/>
-      <c r="D896" s="8"/>
-      <c r="E896" s="18"/>
-      <c r="F896" s="18"/>
-      <c r="G896" s="12"/>
-      <c r="H896" s="13"/>
-    </row>
-    <row r="897" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B896" s="7" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C896" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D896" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E896" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F896" s="18" t="s">
+        <v>1793</v>
+      </c>
+      <c r="G896" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H896" s="40"/>
+      <c r="I896" s="46"/>
+    </row>
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" s="18">
         <v>755</v>
       </c>
-      <c r="B897" s="7"/>
-      <c r="C897" s="8"/>
-      <c r="D897" s="8"/>
-      <c r="E897" s="18"/>
-      <c r="F897" s="18"/>
-      <c r="G897" s="12"/>
-      <c r="H897" s="13"/>
-    </row>
-    <row r="898" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B897" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C897" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D897" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E897" s="18" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F897" s="18" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G897" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="H897" s="40"/>
+      <c r="I897" s="46"/>
+    </row>
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" s="18">
         <v>755</v>
       </c>
-      <c r="B898" s="7"/>
-      <c r="C898" s="8"/>
-      <c r="D898" s="8"/>
-      <c r="E898" s="18"/>
-      <c r="F898" s="18"/>
-      <c r="G898" s="12"/>
-      <c r="H898" s="13"/>
-    </row>
-    <row r="899" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B898" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C898" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D898" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E898" s="18" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F898" s="18" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G898" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="H898" s="40"/>
+      <c r="I898" s="46"/>
+    </row>
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" s="18">
         <v>755</v>
       </c>
-      <c r="B899" s="7"/>
-      <c r="C899" s="8"/>
-      <c r="D899" s="8"/>
-      <c r="E899" s="18"/>
-      <c r="F899" s="18"/>
-      <c r="G899" s="12"/>
-      <c r="H899" s="13"/>
-    </row>
-    <row r="900" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B899" s="7" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C899" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D899" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E899" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F899" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="G899" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H899" s="40"/>
+      <c r="I899" s="46"/>
+    </row>
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" s="18">
         <v>755</v>
       </c>
-      <c r="B900" s="7"/>
-      <c r="C900" s="8"/>
-      <c r="D900" s="8"/>
-      <c r="E900" s="18"/>
-      <c r="F900" s="18"/>
-      <c r="G900" s="12"/>
-      <c r="H900" s="13"/>
-    </row>
-    <row r="901" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B900" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C900" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D900" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E900" s="18" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F900" s="18" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G900" s="12">
+        <v>450000</v>
+      </c>
+      <c r="H900" s="40"/>
+      <c r="I900" s="46"/>
+    </row>
+    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A901" s="18">
         <v>755</v>
       </c>
-      <c r="B901" s="7"/>
-      <c r="C901" s="8"/>
-      <c r="D901" s="8"/>
-      <c r="E901" s="18"/>
-      <c r="F901" s="18"/>
-      <c r="G901" s="12"/>
-      <c r="H901" s="13"/>
-    </row>
-    <row r="902" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B901" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C901" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D901" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E901" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F901" s="18" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G901" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H901" s="40"/>
+      <c r="I901" s="46"/>
+    </row>
+    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" s="18">
         <v>755</v>
       </c>
-      <c r="B902" s="7"/>
-      <c r="C902" s="8"/>
-      <c r="D902" s="8"/>
-      <c r="E902" s="18"/>
-      <c r="F902" s="18"/>
-      <c r="G902" s="12"/>
-      <c r="H902" s="13"/>
-    </row>
-    <row r="903" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B902" s="7" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C902" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D902" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E902" s="18" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F902" s="18" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G902" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="H902" s="40"/>
+      <c r="I902" s="46"/>
+    </row>
+    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903" s="18">
         <v>755</v>
       </c>
-      <c r="B903" s="7"/>
-      <c r="C903" s="8"/>
-      <c r="D903" s="8"/>
-      <c r="E903" s="18"/>
-      <c r="F903" s="18"/>
-      <c r="G903" s="12"/>
-      <c r="H903" s="13"/>
-    </row>
-    <row r="904" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B903" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C903" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D903" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E903" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F903" s="18" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G903" s="12">
+        <v>500000</v>
+      </c>
+      <c r="H903" s="40"/>
+      <c r="I903" s="46"/>
+    </row>
+    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" s="18">
         <v>755</v>
       </c>
-      <c r="B904" s="7"/>
-      <c r="C904" s="8"/>
-      <c r="D904" s="8"/>
-      <c r="E904" s="18"/>
-      <c r="F904" s="18"/>
-      <c r="G904" s="12"/>
-      <c r="H904" s="13"/>
-    </row>
-    <row r="905" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B904" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C904" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D904" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E904" s="18" t="s">
+        <v>439</v>
+      </c>
+      <c r="F904" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="G904" s="12">
+        <v>70000</v>
+      </c>
+      <c r="H904" s="40"/>
+      <c r="I904" s="46"/>
+    </row>
+    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" s="18">
         <v>755</v>
       </c>
-      <c r="B905" s="7"/>
-      <c r="C905" s="8"/>
-      <c r="D905" s="8"/>
-      <c r="E905" s="18"/>
-      <c r="F905" s="18"/>
-      <c r="G905" s="12"/>
-      <c r="H905" s="13"/>
-    </row>
-    <row r="906" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B905" s="7" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C905" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D905" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E905" s="18" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F905" s="18" t="s">
+        <v>1805</v>
+      </c>
+      <c r="G905" s="12">
+        <v>150000</v>
+      </c>
+      <c r="H905" s="40"/>
+      <c r="I905" s="46"/>
+    </row>
+    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A906" s="18">
         <v>755</v>
       </c>
-      <c r="B906" s="7"/>
-      <c r="C906" s="8"/>
-      <c r="D906" s="8"/>
-      <c r="E906" s="18"/>
-      <c r="F906" s="18"/>
-      <c r="G906" s="12"/>
-      <c r="H906" s="13"/>
-    </row>
-    <row r="907" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B906" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C906" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D906" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E906" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F906" s="18" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G906" s="12">
+        <v>140000</v>
+      </c>
+      <c r="H906" s="40"/>
+      <c r="I906" s="46"/>
+    </row>
+    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" s="18">
         <v>755</v>
       </c>
-      <c r="B907" s="7"/>
-      <c r="C907" s="8"/>
-      <c r="D907" s="8"/>
-      <c r="E907" s="18"/>
-      <c r="F907" s="18"/>
-      <c r="G907" s="12"/>
-      <c r="H907" s="13"/>
-    </row>
-    <row r="908" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B907" s="7" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C907" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D907" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E907" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F907" s="18" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G907" s="12">
+        <v>150000</v>
+      </c>
+      <c r="H907" s="40"/>
+      <c r="I907" s="46"/>
+    </row>
+    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908" s="18">
         <v>755</v>
       </c>
-      <c r="B908" s="7"/>
-      <c r="C908" s="8"/>
-      <c r="D908" s="8"/>
-      <c r="E908" s="18"/>
-      <c r="F908" s="18"/>
-      <c r="G908" s="12"/>
-      <c r="H908" s="13"/>
-    </row>
-    <row r="909" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B908" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C908" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D908" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E908" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F908" s="18" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G908" s="12">
+        <v>125000</v>
+      </c>
+      <c r="H908" s="40"/>
+      <c r="I908" s="46"/>
+    </row>
+    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A909" s="18">
         <v>755</v>
       </c>
-      <c r="B909" s="7"/>
-      <c r="C909" s="8"/>
-      <c r="D909" s="8"/>
-      <c r="E909" s="18"/>
-      <c r="F909" s="18"/>
-      <c r="G909" s="12"/>
-      <c r="H909" s="13"/>
-    </row>
-    <row r="910" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B909" s="7" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C909" s="8">
+        <v>46306</v>
+      </c>
+      <c r="D909" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E909" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F909" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G909" s="12">
+        <v>254000</v>
+      </c>
+      <c r="H909" s="40"/>
+      <c r="I909" s="46"/>
+    </row>
+    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910" s="18">
         <v>755</v>
       </c>
@@ -28583,7 +29158,7 @@
       <c r="G910" s="12"/>
       <c r="H910" s="13"/>
     </row>
-    <row r="911" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" s="18">
         <v>755</v>
       </c>
@@ -28595,7 +29170,7 @@
       <c r="G911" s="12"/>
       <c r="H911" s="13"/>
     </row>
-    <row r="912" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" s="18">
         <v>755</v>
       </c>
@@ -28729,239 +29304,252 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="56" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="55" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="54" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="53" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="52" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732:B743 B745">
+    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B744">
+    <cfRule type="duplicateValues" dxfId="51" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
     <cfRule type="duplicateValues" dxfId="49" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="48" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B746:B760">
-    <cfRule type="duplicateValues" dxfId="47" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B761:B762">
-    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B763:B823">
-    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B824">
-    <cfRule type="duplicateValues" dxfId="44" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B825:B832">
-    <cfRule type="duplicateValues" dxfId="43" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833:B835">
-    <cfRule type="duplicateValues" dxfId="42" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836:B840">
-    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841:B844">
-    <cfRule type="duplicateValues" dxfId="40" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="39" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846:B848">
-    <cfRule type="duplicateValues" dxfId="38" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849:B852">
-    <cfRule type="duplicateValues" dxfId="37" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853:B854">
-    <cfRule type="duplicateValues" dxfId="36" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B855:B869">
-    <cfRule type="duplicateValues" dxfId="35" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B876:B879">
-    <cfRule type="duplicateValues" dxfId="34" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="33" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B881:B882">
+    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
-    <cfRule type="expression" dxfId="32" priority="232" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="236" stopIfTrue="1">
       <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="31" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="95" stopIfTrue="1">
       <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="30" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="105" stopIfTrue="1">
       <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="29" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="113" stopIfTrue="1">
       <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="28" priority="309" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="313" stopIfTrue="1">
       <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
-    <cfRule type="expression" dxfId="27" priority="227" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="231" stopIfTrue="1">
       <formula>#REF!&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746:G748">
-    <cfRule type="expression" dxfId="26" priority="401" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="405" stopIfTrue="1">
       <formula>I885:I2745&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G750">
-    <cfRule type="expression" dxfId="25" priority="402" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="406" stopIfTrue="1">
       <formula>I885:I2749&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G753:G755">
-    <cfRule type="expression" dxfId="24" priority="403" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="407" stopIfTrue="1">
       <formula>I885:I2752&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G760">
-    <cfRule type="expression" dxfId="23" priority="404" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="408" stopIfTrue="1">
       <formula>I885:I2756&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G762">
-    <cfRule type="expression" dxfId="22" priority="405" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="409" stopIfTrue="1">
       <formula>I885:I2761&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763 G765">
-    <cfRule type="expression" dxfId="21" priority="668" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="672" stopIfTrue="1">
       <formula>Q762:Q2762&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G767:G775">
-    <cfRule type="expression" dxfId="20" priority="666" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="670" stopIfTrue="1">
       <formula>Q766:Q2766&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G776 G778:G779 G781:G790 G796 G798:G801 G804:G815 G817:G819 G821:G822">
-    <cfRule type="expression" dxfId="19" priority="672" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="676" stopIfTrue="1">
       <formula>Q775:Q2774&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868 G876:G878 G882">
-    <cfRule type="expression" dxfId="18" priority="674" stopIfTrue="1">
+  <conditionalFormatting sqref="G824 G826:G832 G834:G835 G837:G841 G843 G845:G854 G857:G866 G868 G876:G878 G882 G886 G890:G891 G894:G909">
+    <cfRule type="expression" dxfId="20" priority="678" stopIfTrue="1">
       <formula>I824:I2823&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G867:G868">
-    <cfRule type="expression" dxfId="17" priority="690" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="694" stopIfTrue="1">
       <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="16" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="91" stopIfTrue="1">
       <formula>P11:P2015&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="15" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="99" stopIfTrue="1">
       <formula>P52:P2054&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="14" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="109" stopIfTrue="1">
       <formula>P111:P2114&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="13" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="117" stopIfTrue="1">
       <formula>P430:P2431&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="12" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="82" stopIfTrue="1">
       <formula>N541:N2542&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="11" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="125" stopIfTrue="1">
       <formula>P587:P2587&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H744">
-    <cfRule type="expression" dxfId="10" priority="488" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="492" stopIfTrue="1">
       <formula>I885:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H749">
-    <cfRule type="expression" dxfId="9" priority="489" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="493" stopIfTrue="1">
       <formula>I885:I2748&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H751:H752">
-    <cfRule type="expression" dxfId="8" priority="490" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="494" stopIfTrue="1">
       <formula>I885:I2750&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756">
-    <cfRule type="expression" dxfId="7" priority="491" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="495" stopIfTrue="1">
       <formula>I885:I2755&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H761">
-    <cfRule type="expression" dxfId="6" priority="492" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="496" stopIfTrue="1">
       <formula>I885:I2760&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H764 H766">
-    <cfRule type="expression" dxfId="5" priority="670" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="674" stopIfTrue="1">
       <formula>Q763:Q2763&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H777 H780 H791:H795 H797 H802:H803 H816 H820">
-    <cfRule type="expression" dxfId="4" priority="673" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="677" stopIfTrue="1">
       <formula>Q776:Q2775&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H823">
-    <cfRule type="expression" dxfId="3" priority="665" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="669" stopIfTrue="1">
       <formula>Q822:Q2821&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856 H879:H881">
-    <cfRule type="expression" dxfId="2" priority="27" stopIfTrue="1">
+  <conditionalFormatting sqref="H825 H833 H836 H842 H844 H855:H856 H879:H881 H883:H884 H892:H893">
+    <cfRule type="expression" dxfId="4" priority="31" stopIfTrue="1">
       <formula>I825:I2824&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I867">
-    <cfRule type="expression" dxfId="1" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="13" stopIfTrue="1">
       <formula>I865:I2863&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B881:B882">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="B883:B909">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G887:G889">
+    <cfRule type="expression" dxfId="1" priority="728" stopIfTrue="1">
+      <formula>I887:I2887&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G885">
+    <cfRule type="expression" dxfId="0" priority="729" stopIfTrue="1">
+      <formula>I885:I2886&gt;110000000</formula>
+    </cfRule>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="B310" r:id="rId1" display="\\" xr:uid="{F04BB08D-F26B-4EF6-A6AF-EFAD65C2B411}"/>
